--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_utility_general.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_utility_general.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0685888675710359</v>
+        <v>0.06848768983589382</v>
       </c>
       <c r="C2">
-        <v>6230.97768426749</v>
+        <v>6193.472449139794</v>
       </c>
       <c r="D2">
-        <v>5912.37768426749</v>
+        <v>5938.744449139794</v>
       </c>
       <c r="E2">
-        <v>-2738.1</v>
+        <v>-2674.228</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>63.872</v>
       </c>
       <c r="G2">
         <v>318.6</v>
@@ -1445,28 +1445,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.2127616</v>
       </c>
       <c r="N2">
-        <v>414.1333333333333</v>
+        <v>410.9205717333332</v>
       </c>
       <c r="O2">
-        <v>82.82666666666665</v>
+        <v>82.18411434666666</v>
       </c>
       <c r="P2">
-        <v>331.3066666666666</v>
+        <v>328.7364573866666</v>
       </c>
       <c r="Q2">
-        <v>662.9066666666665</v>
+        <v>660.3364573866666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0685888675710359</v>
+        <v>0.06877302003625639</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563937</v>
+        <v>0.4477869201663444</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.9026030855614</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06848768983589382</v>
+        <v>0.06838651210075175</v>
       </c>
       <c r="C3">
-        <v>6193.472449139794</v>
+        <v>6156.203437253726</v>
       </c>
       <c r="D3">
-        <v>5938.744449139794</v>
+        <v>5965.347437253726</v>
       </c>
       <c r="E3">
-        <v>-2674.228</v>
+        <v>-2610.356</v>
       </c>
       <c r="F3">
-        <v>63.872</v>
+        <v>127.744</v>
       </c>
       <c r="G3">
         <v>318.6</v>
@@ -1527,28 +1527,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M3">
-        <v>3.2127616</v>
+        <v>6.4255232</v>
       </c>
       <c r="N3">
-        <v>410.9205717333332</v>
+        <v>407.7078101333333</v>
       </c>
       <c r="O3">
-        <v>82.18411434666666</v>
+        <v>81.54156202666667</v>
       </c>
       <c r="P3">
-        <v>328.7364573866666</v>
+        <v>326.1662481066666</v>
       </c>
       <c r="Q3">
-        <v>660.3364573866666</v>
+        <v>657.7662481066666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06877302003625639</v>
+        <v>0.06896093071505281</v>
       </c>
       <c r="T3">
-        <v>0.4477869201663444</v>
+        <v>0.4514496490540491</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.9026030855614</v>
+        <v>64.45130154278073</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06838651210075175</v>
+        <v>0.06828533436560968</v>
       </c>
       <c r="C4">
-        <v>6156.203437253726</v>
+        <v>6119.173837425456</v>
       </c>
       <c r="D4">
-        <v>5965.347437253726</v>
+        <v>5992.189837425456</v>
       </c>
       <c r="E4">
-        <v>-2610.356</v>
+        <v>-2546.484</v>
       </c>
       <c r="F4">
-        <v>127.744</v>
+        <v>191.616</v>
       </c>
       <c r="G4">
         <v>318.6</v>
@@ -1609,28 +1609,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M4">
-        <v>6.4255232</v>
+        <v>9.638284799999999</v>
       </c>
       <c r="N4">
-        <v>407.7078101333333</v>
+        <v>404.4950485333333</v>
       </c>
       <c r="O4">
-        <v>81.54156202666667</v>
+        <v>80.89900970666666</v>
       </c>
       <c r="P4">
-        <v>326.1662481066666</v>
+        <v>323.5960388266666</v>
       </c>
       <c r="Q4">
-        <v>657.7662481066666</v>
+        <v>655.1960388266666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06896093071505281</v>
+        <v>0.06915271584083472</v>
       </c>
       <c r="T4">
-        <v>0.4514496490540491</v>
+        <v>0.4551878981250055</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.45130154278073</v>
+        <v>42.96753436185382</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06828533436560968</v>
+        <v>0.0681841566304676</v>
       </c>
       <c r="C5">
-        <v>6119.173837425456</v>
+        <v>6082.386896125719</v>
       </c>
       <c r="D5">
-        <v>5992.189837425456</v>
+        <v>6019.274896125718</v>
       </c>
       <c r="E5">
-        <v>-2546.484</v>
+        <v>-2482.612</v>
       </c>
       <c r="F5">
-        <v>191.616</v>
+        <v>255.488</v>
       </c>
       <c r="G5">
         <v>318.6</v>
@@ -1691,28 +1691,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M5">
-        <v>9.638284799999999</v>
+        <v>12.8510464</v>
       </c>
       <c r="N5">
-        <v>404.4950485333333</v>
+        <v>401.2822869333333</v>
       </c>
       <c r="O5">
-        <v>80.89900970666666</v>
+        <v>80.25645738666667</v>
       </c>
       <c r="P5">
-        <v>323.5960388266666</v>
+        <v>321.0258295466666</v>
       </c>
       <c r="Q5">
-        <v>655.1960388266666</v>
+        <v>652.6258295466666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06915271584083472</v>
+        <v>0.06934849649007042</v>
       </c>
       <c r="T5">
-        <v>0.4551878981250055</v>
+        <v>0.4590040273849402</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.96753436185382</v>
+        <v>32.22565077139036</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0681841566304676</v>
+        <v>0.06808297889532554</v>
       </c>
       <c r="C6">
-        <v>6082.386896125719</v>
+        <v>6045.845918788729</v>
       </c>
       <c r="D6">
-        <v>6019.274896125718</v>
+        <v>6046.605918788729</v>
       </c>
       <c r="E6">
-        <v>-2482.612</v>
+        <v>-2418.74</v>
       </c>
       <c r="F6">
-        <v>255.488</v>
+        <v>319.36</v>
       </c>
       <c r="G6">
         <v>318.6</v>
@@ -1773,28 +1773,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M6">
-        <v>12.8510464</v>
+        <v>16.063808</v>
       </c>
       <c r="N6">
-        <v>401.2822869333333</v>
+        <v>398.0695253333333</v>
       </c>
       <c r="O6">
-        <v>80.25645738666667</v>
+        <v>79.61390506666666</v>
       </c>
       <c r="P6">
-        <v>321.0258295466666</v>
+        <v>318.4556202666666</v>
       </c>
       <c r="Q6">
-        <v>652.6258295466666</v>
+        <v>650.0556202666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06934849649007042</v>
+        <v>0.06954839883718478</v>
       </c>
       <c r="T6">
-        <v>0.4590040273849402</v>
+        <v>0.4629004962082418</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.22565077139036</v>
+        <v>25.78052061711228</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06808297889532554</v>
+        <v>0.06798180116018346</v>
       </c>
       <c r="C7">
-        <v>6045.845918788729</v>
+        <v>6009.554271156952</v>
       </c>
       <c r="D7">
-        <v>6046.605918788729</v>
+        <v>6074.186271156952</v>
       </c>
       <c r="E7">
-        <v>-2418.74</v>
+        <v>-2354.868</v>
       </c>
       <c r="F7">
-        <v>319.36</v>
+        <v>383.232</v>
       </c>
       <c r="G7">
         <v>318.6</v>
@@ -1855,28 +1855,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M7">
-        <v>16.063808</v>
+        <v>19.2765696</v>
       </c>
       <c r="N7">
-        <v>398.0695253333333</v>
+        <v>394.8567637333333</v>
       </c>
       <c r="O7">
-        <v>79.61390506666666</v>
+        <v>78.97135274666665</v>
       </c>
       <c r="P7">
-        <v>318.4556202666666</v>
+        <v>315.8854109866666</v>
       </c>
       <c r="Q7">
-        <v>650.0556202666667</v>
+        <v>647.4854109866666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06954839883718478</v>
+        <v>0.06975255442572709</v>
       </c>
       <c r="T7">
-        <v>0.4629004962082418</v>
+        <v>0.4668798686235288</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.78052061711228</v>
+        <v>21.4837671809269</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06798180116018346</v>
+        <v>0.06788062342504139</v>
       </c>
       <c r="C8">
-        <v>6009.554271156952</v>
+        <v>5973.515380662805</v>
       </c>
       <c r="D8">
-        <v>6074.186271156952</v>
+        <v>6102.019380662805</v>
       </c>
       <c r="E8">
-        <v>-2354.868</v>
+        <v>-2290.996</v>
       </c>
       <c r="F8">
-        <v>383.232</v>
+        <v>447.1039999999999</v>
       </c>
       <c r="G8">
         <v>318.6</v>
@@ -1937,28 +1937,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M8">
-        <v>19.2765696</v>
+        <v>22.4893312</v>
       </c>
       <c r="N8">
-        <v>394.8567637333333</v>
+        <v>391.6440021333333</v>
       </c>
       <c r="O8">
-        <v>78.97135274666665</v>
+        <v>78.32880042666666</v>
       </c>
       <c r="P8">
-        <v>315.8854109866666</v>
+        <v>313.3152017066666</v>
       </c>
       <c r="Q8">
-        <v>647.4854109866666</v>
+        <v>644.9152017066666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06975255442572709</v>
+        <v>0.06996110045703376</v>
       </c>
       <c r="T8">
-        <v>0.4668798686235288</v>
+        <v>0.4709448189402196</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.4837671809269</v>
+        <v>18.41465758365164</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06788062342504138</v>
+        <v>0.06777944568989933</v>
       </c>
       <c r="C9">
-        <v>5973.51538066281</v>
+        <v>5937.73273784856</v>
       </c>
       <c r="D9">
-        <v>6102.019380662809</v>
+        <v>6130.108737848559</v>
       </c>
       <c r="E9">
-        <v>-2290.996</v>
+        <v>-2227.124</v>
       </c>
       <c r="F9">
-        <v>447.104</v>
+        <v>510.976</v>
       </c>
       <c r="G9">
         <v>318.6</v>
@@ -2019,28 +2019,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M9">
-        <v>22.4893312</v>
+        <v>25.7020928</v>
       </c>
       <c r="N9">
-        <v>391.6440021333333</v>
+        <v>388.4312405333333</v>
       </c>
       <c r="O9">
-        <v>78.32880042666666</v>
+        <v>77.68624810666665</v>
       </c>
       <c r="P9">
-        <v>313.3152017066666</v>
+        <v>310.7449924266666</v>
       </c>
       <c r="Q9">
-        <v>644.9152017066666</v>
+        <v>642.3449924266665</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06996110045703376</v>
+        <v>0.07017418009771666</v>
       </c>
       <c r="T9">
-        <v>0.4709448189402196</v>
+        <v>0.4750981377420559</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.41465758365163</v>
+        <v>16.11282538569518</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06777944568989933</v>
+        <v>0.06767826795475725</v>
       </c>
       <c r="C10">
-        <v>5937.73273784856</v>
+        <v>5902.20989782561</v>
       </c>
       <c r="D10">
-        <v>6130.108737848559</v>
+        <v>6158.45789782561</v>
       </c>
       <c r="E10">
-        <v>-2227.124</v>
+        <v>-2163.252</v>
       </c>
       <c r="F10">
-        <v>510.976</v>
+        <v>574.848</v>
       </c>
       <c r="G10">
         <v>318.6</v>
@@ -2101,28 +2101,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M10">
-        <v>25.7020928</v>
+        <v>28.9148544</v>
       </c>
       <c r="N10">
-        <v>388.4312405333333</v>
+        <v>385.2184789333332</v>
       </c>
       <c r="O10">
-        <v>77.68624810666665</v>
+        <v>77.04369578666666</v>
       </c>
       <c r="P10">
-        <v>310.7449924266666</v>
+        <v>308.1747831466666</v>
       </c>
       <c r="Q10">
-        <v>642.3449924266665</v>
+        <v>639.7747831466666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07017418009771666</v>
+        <v>0.07039194280742554</v>
       </c>
       <c r="T10">
-        <v>0.4750981377420559</v>
+        <v>0.4793427382758007</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.11282538569518</v>
+        <v>14.32251145395127</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06767826795475725</v>
+        <v>0.06757709021961518</v>
       </c>
       <c r="C11">
-        <v>5902.20989782561</v>
+        <v>5866.95048177443</v>
       </c>
       <c r="D11">
-        <v>6158.45789782561</v>
+        <v>6187.07048177443</v>
       </c>
       <c r="E11">
-        <v>-2163.252</v>
+        <v>-2099.38</v>
       </c>
       <c r="F11">
-        <v>574.848</v>
+        <v>638.7199999999999</v>
       </c>
       <c r="G11">
         <v>318.6</v>
@@ -2183,28 +2183,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M11">
-        <v>28.9148544</v>
+        <v>32.127616</v>
       </c>
       <c r="N11">
-        <v>385.2184789333332</v>
+        <v>382.0057173333333</v>
       </c>
       <c r="O11">
-        <v>77.04369578666666</v>
+        <v>76.40114346666665</v>
       </c>
       <c r="P11">
-        <v>308.1747831466666</v>
+        <v>305.6045738666666</v>
       </c>
       <c r="Q11">
-        <v>639.7747831466666</v>
+        <v>637.2045738666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07039194280742554</v>
+        <v>0.0706145446884613</v>
       </c>
       <c r="T11">
-        <v>0.4793427382758007</v>
+        <v>0.4836816632658509</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.32251145395127</v>
+        <v>12.89026030855614</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06757709021961519</v>
+        <v>0.06760791248447311</v>
       </c>
       <c r="C12">
-        <v>5866.950481774426</v>
+        <v>5794.333971027714</v>
       </c>
       <c r="D12">
-        <v>6187.070481774426</v>
+        <v>6178.325971027713</v>
       </c>
       <c r="E12">
-        <v>-2099.38</v>
+        <v>-2035.508</v>
       </c>
       <c r="F12">
-        <v>638.72</v>
+        <v>702.592</v>
       </c>
       <c r="G12">
         <v>318.6</v>
@@ -2265,45 +2265,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M12">
-        <v>32.127616</v>
+        <v>36.3942656</v>
       </c>
       <c r="N12">
-        <v>382.0057173333333</v>
+        <v>377.7390677333333</v>
       </c>
       <c r="O12">
-        <v>76.40114346666665</v>
+        <v>75.54781354666666</v>
       </c>
       <c r="P12">
-        <v>305.6045738666666</v>
+        <v>302.1912541866666</v>
       </c>
       <c r="Q12">
-        <v>637.2045738666666</v>
+        <v>633.7912541866666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07061454468846132</v>
+        <v>0.07084214885895854</v>
       </c>
       <c r="T12">
-        <v>0.483681663265851</v>
+        <v>0.4881180921882618</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>12.89026030855614</v>
+        <v>11.37908202036459</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06760791248447311</v>
+        <v>0.06751873474933104</v>
       </c>
       <c r="C13">
-        <v>5794.333971027714</v>
+        <v>5755.83035106572</v>
       </c>
       <c r="D13">
-        <v>6178.325971027713</v>
+        <v>6203.694351065719</v>
       </c>
       <c r="E13">
-        <v>-2035.508</v>
+        <v>-1971.636</v>
       </c>
       <c r="F13">
-        <v>702.592</v>
+        <v>766.4639999999999</v>
       </c>
       <c r="G13">
         <v>318.6</v>
@@ -2347,28 +2347,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M13">
-        <v>36.3942656</v>
+        <v>39.7028352</v>
       </c>
       <c r="N13">
-        <v>377.7390677333333</v>
+        <v>374.4304981333333</v>
       </c>
       <c r="O13">
-        <v>75.54781354666666</v>
+        <v>74.88609962666666</v>
       </c>
       <c r="P13">
-        <v>302.1912541866666</v>
+        <v>299.5443985066667</v>
       </c>
       <c r="Q13">
-        <v>633.7912541866666</v>
+        <v>631.1443985066667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07084214885895854</v>
+        <v>0.07107492585151254</v>
       </c>
       <c r="T13">
-        <v>0.4881180921882618</v>
+        <v>0.4926553490407276</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.37908202036459</v>
+        <v>10.4308251853342</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06751873474933104</v>
+        <v>0.06760635701418898</v>
       </c>
       <c r="C14">
-        <v>5755.83035106572</v>
+        <v>5667.030677489934</v>
       </c>
       <c r="D14">
-        <v>6203.694351065719</v>
+        <v>6178.766677489933</v>
       </c>
       <c r="E14">
-        <v>-1971.636</v>
+        <v>-1907.764</v>
       </c>
       <c r="F14">
-        <v>766.4639999999999</v>
+        <v>830.336</v>
       </c>
       <c r="G14">
         <v>318.6</v>
@@ -2429,45 +2429,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M14">
-        <v>39.7028352</v>
+        <v>44.422976</v>
       </c>
       <c r="N14">
-        <v>374.4304981333333</v>
+        <v>369.7103573333333</v>
       </c>
       <c r="O14">
-        <v>74.88609962666666</v>
+        <v>73.94207146666666</v>
       </c>
       <c r="P14">
-        <v>299.5443985066667</v>
+        <v>295.7682858666666</v>
       </c>
       <c r="Q14">
-        <v>631.1443985066667</v>
+        <v>627.3682858666666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07107492585151254</v>
+        <v>0.07131305403929766</v>
       </c>
       <c r="T14">
-        <v>0.4926553490407276</v>
+        <v>0.4972969106484224</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.4308251853342</v>
+        <v>9.32250314191767</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06760635701418898</v>
+        <v>0.0675307792790469</v>
       </c>
       <c r="C15">
-        <v>5667.030677489934</v>
+        <v>5624.647883443367</v>
       </c>
       <c r="D15">
-        <v>6178.766677489933</v>
+        <v>6200.255883443367</v>
       </c>
       <c r="E15">
-        <v>-1907.764</v>
+        <v>-1843.892</v>
       </c>
       <c r="F15">
-        <v>830.336</v>
+        <v>894.2080000000001</v>
       </c>
       <c r="G15">
         <v>318.6</v>
@@ -2511,28 +2511,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M15">
-        <v>44.422976</v>
+        <v>47.840128</v>
       </c>
       <c r="N15">
-        <v>369.7103573333333</v>
+        <v>366.2932053333333</v>
       </c>
       <c r="O15">
-        <v>73.94207146666666</v>
+        <v>73.25864106666666</v>
       </c>
       <c r="P15">
-        <v>295.7682858666666</v>
+        <v>293.0345642666666</v>
       </c>
       <c r="Q15">
-        <v>627.3682858666666</v>
+        <v>624.6345642666665</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07131305403929766</v>
+        <v>0.07155672009191499</v>
       </c>
       <c r="T15">
-        <v>0.4972969106484224</v>
+        <v>0.5020464155493194</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.32250314191767</v>
+        <v>8.656610060352122</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0675307792790469</v>
+        <v>0.06745520154390482</v>
       </c>
       <c r="C16">
-        <v>5624.647883443367</v>
+        <v>5582.415086201278</v>
       </c>
       <c r="D16">
-        <v>6200.255883443367</v>
+        <v>6221.895086201278</v>
       </c>
       <c r="E16">
-        <v>-1843.892</v>
+        <v>-1780.02</v>
       </c>
       <c r="F16">
-        <v>894.2080000000001</v>
+        <v>958.0800000000002</v>
       </c>
       <c r="G16">
         <v>318.6</v>
@@ -2593,28 +2593,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M16">
-        <v>47.840128</v>
+        <v>51.25728000000001</v>
       </c>
       <c r="N16">
-        <v>366.2932053333333</v>
+        <v>362.8760533333333</v>
       </c>
       <c r="O16">
-        <v>73.25864106666666</v>
+        <v>72.57521066666666</v>
       </c>
       <c r="P16">
-        <v>293.0345642666666</v>
+        <v>290.3008426666667</v>
       </c>
       <c r="Q16">
-        <v>624.6345642666665</v>
+        <v>621.9008426666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07155672009191499</v>
+        <v>0.07180611946341743</v>
       </c>
       <c r="T16">
-        <v>0.5020464155493194</v>
+        <v>0.5069076735067081</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.656610060352122</v>
+        <v>8.079502722995315</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06745520154390482</v>
+        <v>0.06748202380876275</v>
       </c>
       <c r="C17">
-        <v>5582.415086201278</v>
+        <v>5510.846142438448</v>
       </c>
       <c r="D17">
-        <v>6221.895086201278</v>
+        <v>6214.198142438448</v>
       </c>
       <c r="E17">
-        <v>-1780.02</v>
+        <v>-1716.148</v>
       </c>
       <c r="F17">
-        <v>958.0799999999999</v>
+        <v>1021.952</v>
       </c>
       <c r="G17">
         <v>318.6</v>
@@ -2675,45 +2675,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M17">
-        <v>51.25727999999999</v>
+        <v>55.4919936</v>
       </c>
       <c r="N17">
-        <v>362.8760533333333</v>
+        <v>358.6413397333333</v>
       </c>
       <c r="O17">
-        <v>72.57521066666666</v>
+        <v>71.72826794666666</v>
       </c>
       <c r="P17">
-        <v>290.3008426666667</v>
+        <v>286.9130717866666</v>
       </c>
       <c r="Q17">
-        <v>621.9008426666667</v>
+        <v>618.5130717866666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07180611946341743</v>
+        <v>0.07206145691519375</v>
       </c>
       <c r="T17">
-        <v>0.5069076735067081</v>
+        <v>0.5118846757011775</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.079502722995315</v>
+        <v>7.462938461330271</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06748202380876275</v>
+        <v>0.06741284607362066</v>
       </c>
       <c r="C18">
-        <v>5510.846142438448</v>
+        <v>5466.86435734831</v>
       </c>
       <c r="D18">
-        <v>6214.198142438448</v>
+        <v>6234.08835734831</v>
       </c>
       <c r="E18">
-        <v>-1716.148</v>
+        <v>-1652.276</v>
       </c>
       <c r="F18">
-        <v>1021.952</v>
+        <v>1085.824</v>
       </c>
       <c r="G18">
         <v>318.6</v>
@@ -2757,28 +2757,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M18">
-        <v>55.4919936</v>
+        <v>58.96024320000001</v>
       </c>
       <c r="N18">
-        <v>358.6413397333333</v>
+        <v>355.1730901333333</v>
       </c>
       <c r="O18">
-        <v>71.72826794666666</v>
+        <v>71.03461802666666</v>
       </c>
       <c r="P18">
-        <v>286.9130717866666</v>
+        <v>284.1384721066667</v>
       </c>
       <c r="Q18">
-        <v>618.5130717866666</v>
+        <v>615.7384721066667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07206145691519375</v>
+        <v>0.07232294707665141</v>
       </c>
       <c r="T18">
-        <v>0.5118846757011775</v>
+        <v>0.516981605659369</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.462938461330271</v>
+        <v>7.02394208125202</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06741284607362066</v>
+        <v>0.0673436683384786</v>
       </c>
       <c r="C19">
-        <v>5466.86435734831</v>
+        <v>5423.010309094559</v>
       </c>
       <c r="D19">
-        <v>6234.08835734831</v>
+        <v>6254.106309094558</v>
       </c>
       <c r="E19">
-        <v>-1652.276</v>
+        <v>-1588.404</v>
       </c>
       <c r="F19">
-        <v>1085.824</v>
+        <v>1149.696</v>
       </c>
       <c r="G19">
         <v>318.6</v>
@@ -2839,28 +2839,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M19">
-        <v>58.96024320000001</v>
+        <v>62.42849280000001</v>
       </c>
       <c r="N19">
-        <v>355.1730901333333</v>
+        <v>351.7048405333333</v>
       </c>
       <c r="O19">
-        <v>71.03461802666666</v>
+        <v>70.34096810666665</v>
       </c>
       <c r="P19">
-        <v>284.1384721066667</v>
+        <v>281.3638724266666</v>
       </c>
       <c r="Q19">
-        <v>615.7384721066667</v>
+        <v>612.9638724266665</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07232294707665141</v>
+        <v>0.07259081504692513</v>
       </c>
       <c r="T19">
-        <v>0.516981605659369</v>
+        <v>0.5222028509823946</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.02394208125202</v>
+        <v>6.633723076738018</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0673436683384786</v>
+        <v>0.06727449060333654</v>
       </c>
       <c r="C20">
-        <v>5423.010309094559</v>
+        <v>5379.285232148167</v>
       </c>
       <c r="D20">
-        <v>6254.106309094558</v>
+        <v>6274.253232148167</v>
       </c>
       <c r="E20">
-        <v>-1588.404</v>
+        <v>-1524.532</v>
       </c>
       <c r="F20">
-        <v>1149.696</v>
+        <v>1213.568</v>
       </c>
       <c r="G20">
         <v>318.6</v>
@@ -2921,28 +2921,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M20">
-        <v>62.42849279999999</v>
+        <v>65.89674239999999</v>
       </c>
       <c r="N20">
-        <v>351.7048405333333</v>
+        <v>348.2365909333333</v>
       </c>
       <c r="O20">
-        <v>70.34096810666665</v>
+        <v>69.64731818666665</v>
       </c>
       <c r="P20">
-        <v>281.3638724266666</v>
+        <v>278.5892727466666</v>
       </c>
       <c r="Q20">
-        <v>612.9638724266665</v>
+        <v>610.1892727466666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07259081504692512</v>
+        <v>0.07286529704115621</v>
       </c>
       <c r="T20">
-        <v>0.5222028509823945</v>
+        <v>0.5275530159430256</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.633723076738019</v>
+        <v>6.284579756909703</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06727449060333654</v>
+        <v>0.06736531286819446</v>
       </c>
       <c r="C21">
-        <v>5379.285232148167</v>
+        <v>5288.989229291419</v>
       </c>
       <c r="D21">
-        <v>6274.253232148167</v>
+        <v>6247.829229291419</v>
       </c>
       <c r="E21">
-        <v>-1524.532</v>
+        <v>-1460.66</v>
       </c>
       <c r="F21">
-        <v>1213.568</v>
+        <v>1277.44</v>
       </c>
       <c r="G21">
         <v>318.6</v>
@@ -3003,45 +3003,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M21">
-        <v>65.89674239999999</v>
+        <v>70.642432</v>
       </c>
       <c r="N21">
-        <v>348.2365909333333</v>
+        <v>343.4909013333333</v>
       </c>
       <c r="O21">
-        <v>69.64731818666665</v>
+        <v>68.69818026666665</v>
       </c>
       <c r="P21">
-        <v>278.5892727466666</v>
+        <v>274.7927210666666</v>
       </c>
       <c r="Q21">
-        <v>610.1892727466666</v>
+        <v>606.3927210666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07286529704115621</v>
+        <v>0.07314664108524307</v>
       </c>
       <c r="T21">
-        <v>0.5275530159430256</v>
+        <v>0.5330369350276725</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.284579756909703</v>
+        <v>5.862387825681501</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06736531286819446</v>
+        <v>0.0673041351330524</v>
       </c>
       <c r="C22">
-        <v>5288.989229291419</v>
+        <v>5242.891859121331</v>
       </c>
       <c r="D22">
-        <v>6247.829229291419</v>
+        <v>6265.60385912133</v>
       </c>
       <c r="E22">
-        <v>-1460.66</v>
+        <v>-1396.788</v>
       </c>
       <c r="F22">
-        <v>1277.44</v>
+        <v>1341.312</v>
       </c>
       <c r="G22">
         <v>318.6</v>
@@ -3085,28 +3085,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M22">
-        <v>70.642432</v>
+        <v>74.17455360000001</v>
       </c>
       <c r="N22">
-        <v>343.4909013333333</v>
+        <v>339.9587797333332</v>
       </c>
       <c r="O22">
-        <v>68.69818026666665</v>
+        <v>67.99175594666666</v>
       </c>
       <c r="P22">
-        <v>274.7927210666666</v>
+        <v>271.9670237866666</v>
       </c>
       <c r="Q22">
-        <v>606.3927210666666</v>
+        <v>603.5670237866666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07314664108524307</v>
+        <v>0.07343510776335746</v>
       </c>
       <c r="T22">
-        <v>0.5330369350276725</v>
+        <v>0.5386596875068673</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.862387825681501</v>
+        <v>5.583226500649047</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0673041351330524</v>
+        <v>0.06724295739791031</v>
       </c>
       <c r="C23">
-        <v>5242.891859121331</v>
+        <v>5196.895912609922</v>
       </c>
       <c r="D23">
-        <v>6265.60385912133</v>
+        <v>6283.479912609921</v>
       </c>
       <c r="E23">
-        <v>-1396.788</v>
+        <v>-1332.916</v>
       </c>
       <c r="F23">
-        <v>1341.312</v>
+        <v>1405.184</v>
       </c>
       <c r="G23">
         <v>318.6</v>
@@ -3167,28 +3167,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M23">
-        <v>74.1745536</v>
+        <v>77.70667520000001</v>
       </c>
       <c r="N23">
-        <v>339.9587797333332</v>
+        <v>336.4266581333333</v>
       </c>
       <c r="O23">
-        <v>67.99175594666666</v>
+        <v>67.28533162666666</v>
       </c>
       <c r="P23">
-        <v>271.9670237866666</v>
+        <v>269.1413265066666</v>
       </c>
       <c r="Q23">
-        <v>603.5670237866666</v>
+        <v>600.7413265066666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07343510776335746</v>
+        <v>0.07373097102296194</v>
       </c>
       <c r="T23">
-        <v>0.5386596875068673</v>
+        <v>0.5444266131265544</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.583226500649048</v>
+        <v>5.329443477892273</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06724295739791031</v>
+        <v>0.06718177966276824</v>
       </c>
       <c r="C24">
-        <v>5196.895912609922</v>
+        <v>5151.002260339952</v>
       </c>
       <c r="D24">
-        <v>6283.479912609921</v>
+        <v>6301.458260339952</v>
       </c>
       <c r="E24">
-        <v>-1332.916</v>
+        <v>-1269.044</v>
       </c>
       <c r="F24">
-        <v>1405.184</v>
+        <v>1469.056</v>
       </c>
       <c r="G24">
         <v>318.6</v>
@@ -3249,28 +3249,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M24">
-        <v>77.70667520000001</v>
+        <v>81.2387968</v>
       </c>
       <c r="N24">
-        <v>336.4266581333333</v>
+        <v>332.8945365333333</v>
       </c>
       <c r="O24">
-        <v>67.28533162666666</v>
+        <v>66.57890730666666</v>
       </c>
       <c r="P24">
-        <v>269.1413265066666</v>
+        <v>266.3156292266666</v>
       </c>
       <c r="Q24">
-        <v>600.7413265066666</v>
+        <v>597.9156292266666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07373097102296194</v>
+        <v>0.07403451904255616</v>
       </c>
       <c r="T24">
-        <v>0.5444266131265544</v>
+        <v>0.5503433290220774</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.329443477892273</v>
+        <v>5.09772854407087</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06718177966276824</v>
+        <v>0.06712060192762617</v>
       </c>
       <c r="C25">
-        <v>5151.002260339952</v>
+        <v>5105.211782886478</v>
       </c>
       <c r="D25">
-        <v>6301.458260339952</v>
+        <v>6319.539782886477</v>
       </c>
       <c r="E25">
-        <v>-1269.044</v>
+        <v>-1205.172</v>
       </c>
       <c r="F25">
-        <v>1469.056</v>
+        <v>1532.928</v>
       </c>
       <c r="G25">
         <v>318.6</v>
@@ -3331,28 +3331,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M25">
-        <v>81.2387968</v>
+        <v>84.77091840000001</v>
       </c>
       <c r="N25">
-        <v>332.8945365333333</v>
+        <v>329.3624149333332</v>
       </c>
       <c r="O25">
-        <v>66.57890730666666</v>
+        <v>65.87248298666665</v>
       </c>
       <c r="P25">
-        <v>266.3156292266666</v>
+        <v>263.4899319466666</v>
       </c>
       <c r="Q25">
-        <v>597.9156292266666</v>
+        <v>595.0899319466666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07403451904255616</v>
+        <v>0.07434605516792918</v>
       </c>
       <c r="T25">
-        <v>0.5503433290220774</v>
+        <v>0.5564157479674827</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.09772854407087</v>
+        <v>4.885323188067916</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06712060192762617</v>
+        <v>0.06705942419248409</v>
       </c>
       <c r="C26">
-        <v>5105.211782886478</v>
+        <v>5059.525370960587</v>
       </c>
       <c r="D26">
-        <v>6319.539782886477</v>
+        <v>6337.725370960587</v>
       </c>
       <c r="E26">
-        <v>-1205.172</v>
+        <v>-1141.3</v>
       </c>
       <c r="F26">
-        <v>1532.928</v>
+        <v>1596.8</v>
       </c>
       <c r="G26">
         <v>318.6</v>
@@ -3413,28 +3413,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M26">
-        <v>84.7709184</v>
+        <v>88.30304</v>
       </c>
       <c r="N26">
-        <v>329.3624149333333</v>
+        <v>325.8302933333333</v>
       </c>
       <c r="O26">
-        <v>65.87248298666667</v>
+        <v>65.16605866666666</v>
       </c>
       <c r="P26">
-        <v>263.4899319466666</v>
+        <v>260.6642346666666</v>
       </c>
       <c r="Q26">
-        <v>595.0899319466666</v>
+        <v>592.2642346666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07434605516792916</v>
+        <v>0.07466589892331213</v>
       </c>
       <c r="T26">
-        <v>0.5564157479674826</v>
+        <v>0.5626500980847653</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.885323188067918</v>
+        <v>4.689910260545201</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06705942419248409</v>
+        <v>0.06699824645734202</v>
       </c>
       <c r="C27">
-        <v>5059.525370960587</v>
+        <v>5013.943925555659</v>
       </c>
       <c r="D27">
-        <v>6337.725370960587</v>
+        <v>6356.015925555658</v>
       </c>
       <c r="E27">
-        <v>-1141.3</v>
+        <v>-1077.428</v>
       </c>
       <c r="F27">
-        <v>1596.8</v>
+        <v>1660.672</v>
       </c>
       <c r="G27">
         <v>318.6</v>
@@ -3495,28 +3495,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M27">
-        <v>88.30304</v>
+        <v>91.83516160000001</v>
       </c>
       <c r="N27">
-        <v>325.8302933333333</v>
+        <v>322.2981717333333</v>
       </c>
       <c r="O27">
-        <v>65.16605866666666</v>
+        <v>64.45963434666666</v>
       </c>
       <c r="P27">
-        <v>260.6642346666666</v>
+        <v>257.8385373866666</v>
       </c>
       <c r="Q27">
-        <v>592.2642346666667</v>
+        <v>589.4385373866667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07466589892331213</v>
+        <v>0.07499438710451625</v>
       </c>
       <c r="T27">
-        <v>0.5626500980847653</v>
+        <v>0.5690529441511638</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.689910260545201</v>
+        <v>4.509529096678078</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06699824645734202</v>
+        <v>0.06747706872219995</v>
       </c>
       <c r="C28">
-        <v>5013.943925555659</v>
+        <v>4809.674624612898</v>
       </c>
       <c r="D28">
-        <v>6356.015925555658</v>
+        <v>6215.618624612897</v>
       </c>
       <c r="E28">
-        <v>-1077.428</v>
+        <v>-1013.556</v>
       </c>
       <c r="F28">
-        <v>1660.672</v>
+        <v>1724.544</v>
       </c>
       <c r="G28">
         <v>318.6</v>
@@ -3577,45 +3577,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M28">
-        <v>91.83516160000001</v>
+        <v>99.67864320000001</v>
       </c>
       <c r="N28">
-        <v>322.2981717333333</v>
+        <v>314.4546901333333</v>
       </c>
       <c r="O28">
-        <v>64.45963434666666</v>
+        <v>62.89093802666665</v>
       </c>
       <c r="P28">
-        <v>257.8385373866666</v>
+        <v>251.5637521066666</v>
       </c>
       <c r="Q28">
-        <v>589.4385373866667</v>
+        <v>583.1637521066666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07499438710451625</v>
+        <v>0.07533187496191775</v>
       </c>
       <c r="T28">
-        <v>0.5690529441511638</v>
+        <v>0.5756312106577376</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.509529096678078</v>
+        <v>4.154684695119659</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06747706872219995</v>
+        <v>0.06743589098705788</v>
       </c>
       <c r="C29">
-        <v>4809.674624612898</v>
+        <v>4757.632278294436</v>
       </c>
       <c r="D29">
-        <v>6215.618624612897</v>
+        <v>6227.448278294436</v>
       </c>
       <c r="E29">
-        <v>-1013.556</v>
+        <v>-949.6839999999997</v>
       </c>
       <c r="F29">
-        <v>1724.544</v>
+        <v>1788.416</v>
       </c>
       <c r="G29">
         <v>318.6</v>
@@ -3659,28 +3659,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M29">
-        <v>99.67864320000001</v>
+        <v>103.3704448</v>
       </c>
       <c r="N29">
-        <v>314.4546901333333</v>
+        <v>310.7628885333332</v>
       </c>
       <c r="O29">
-        <v>62.89093802666665</v>
+        <v>62.15257770666665</v>
       </c>
       <c r="P29">
-        <v>251.5637521066666</v>
+        <v>248.6103108266666</v>
       </c>
       <c r="Q29">
-        <v>583.1637521066666</v>
+        <v>580.2103108266665</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07533187496191775</v>
+        <v>0.07567873748202483</v>
       </c>
       <c r="T29">
-        <v>0.5756312106577376</v>
+        <v>0.582392206789494</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.154684695119659</v>
+        <v>4.006303098865384</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06743589098705788</v>
+        <v>0.06820671325191582</v>
       </c>
       <c r="C30">
-        <v>4757.632278294436</v>
+        <v>4479.527350323611</v>
       </c>
       <c r="D30">
-        <v>6227.448278294436</v>
+        <v>6013.215350323611</v>
       </c>
       <c r="E30">
-        <v>-949.6839999999997</v>
+        <v>-885.8119999999997</v>
       </c>
       <c r="F30">
-        <v>1788.416</v>
+        <v>1852.288</v>
       </c>
       <c r="G30">
         <v>318.6</v>
@@ -3741,45 +3741,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M30">
-        <v>103.3704448</v>
+        <v>113.5452544</v>
       </c>
       <c r="N30">
-        <v>310.7628885333332</v>
+        <v>300.5880789333332</v>
       </c>
       <c r="O30">
-        <v>62.15257770666665</v>
+        <v>60.11761578666665</v>
       </c>
       <c r="P30">
-        <v>248.6103108266666</v>
+        <v>240.4704631466666</v>
       </c>
       <c r="Q30">
-        <v>580.2103108266665</v>
+        <v>572.0704631466665</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07567873748202483</v>
+        <v>0.07603537077734622</v>
       </c>
       <c r="T30">
-        <v>0.582392206789494</v>
+        <v>0.5893436535165111</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.006303098865384</v>
+        <v>3.647297595321898</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06820671325191581</v>
+        <v>0.06819353551677373</v>
       </c>
       <c r="C31">
-        <v>4479.527350323616</v>
+        <v>4419.193896489292</v>
       </c>
       <c r="D31">
-        <v>6013.215350323615</v>
+        <v>6016.753896489292</v>
       </c>
       <c r="E31">
-        <v>-885.8120000000001</v>
+        <v>-821.9400000000001</v>
       </c>
       <c r="F31">
-        <v>1852.288</v>
+        <v>1916.16</v>
       </c>
       <c r="G31">
         <v>318.6</v>
@@ -3823,28 +3823,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M31">
-        <v>113.5452544</v>
+        <v>117.460608</v>
       </c>
       <c r="N31">
-        <v>300.5880789333333</v>
+        <v>296.6727253333333</v>
       </c>
       <c r="O31">
-        <v>60.11761578666666</v>
+        <v>59.33454506666666</v>
       </c>
       <c r="P31">
-        <v>240.4704631466666</v>
+        <v>237.3381802666666</v>
       </c>
       <c r="Q31">
-        <v>572.0704631466666</v>
+        <v>568.9381802666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07603537077734622</v>
+        <v>0.07640219359539106</v>
       </c>
       <c r="T31">
-        <v>0.5893436535165111</v>
+        <v>0.5964937130071573</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.647297595321899</v>
+        <v>3.525721008811169</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06819353551677373</v>
+        <v>0.06887475778163166</v>
       </c>
       <c r="C32">
-        <v>4419.193896489292</v>
+        <v>4177.692871940141</v>
       </c>
       <c r="D32">
-        <v>6016.753896489292</v>
+        <v>5839.124871940141</v>
       </c>
       <c r="E32">
-        <v>-821.9400000000001</v>
+        <v>-758.068</v>
       </c>
       <c r="F32">
-        <v>1916.16</v>
+        <v>1980.032</v>
       </c>
       <c r="G32">
         <v>318.6</v>
@@ -3905,45 +3905,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M32">
-        <v>117.460608</v>
+        <v>126.9200512</v>
       </c>
       <c r="N32">
-        <v>296.6727253333333</v>
+        <v>287.2132821333333</v>
       </c>
       <c r="O32">
-        <v>59.33454506666666</v>
+        <v>57.44265642666666</v>
       </c>
       <c r="P32">
-        <v>237.3381802666666</v>
+        <v>229.7706257066666</v>
       </c>
       <c r="Q32">
-        <v>568.9381802666666</v>
+        <v>561.3706257066666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07640219359539106</v>
+        <v>0.07677964895888648</v>
       </c>
       <c r="T32">
-        <v>0.5964937130071573</v>
+        <v>0.6038510205989815</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.525721008811169</v>
+        <v>3.262946472348518</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06887475778163166</v>
+        <v>0.0688839800464896</v>
       </c>
       <c r="C33">
-        <v>4177.692871940141</v>
+        <v>4111.488087212412</v>
       </c>
       <c r="D33">
-        <v>5839.124871940141</v>
+        <v>5836.792087212412</v>
       </c>
       <c r="E33">
-        <v>-758.068</v>
+        <v>-694.1959999999999</v>
       </c>
       <c r="F33">
-        <v>1980.032</v>
+        <v>2043.904</v>
       </c>
       <c r="G33">
         <v>318.6</v>
@@ -3987,28 +3987,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M33">
-        <v>126.9200512</v>
+        <v>131.0142464</v>
       </c>
       <c r="N33">
-        <v>287.2132821333333</v>
+        <v>283.1190869333333</v>
       </c>
       <c r="O33">
-        <v>57.44265642666666</v>
+        <v>56.62381738666666</v>
       </c>
       <c r="P33">
-        <v>229.7706257066666</v>
+        <v>226.4952695466666</v>
       </c>
       <c r="Q33">
-        <v>561.3706257066666</v>
+        <v>558.0952695466666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07677964895888648</v>
+        <v>0.07716820595071999</v>
       </c>
       <c r="T33">
-        <v>0.6038510205989815</v>
+        <v>0.6114247195905654</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.262946472348518</v>
+        <v>3.160979395087626</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0688839800464896</v>
+        <v>0.06889320231134753</v>
       </c>
       <c r="C34">
-        <v>4111.488087212412</v>
+        <v>4045.285165678742</v>
       </c>
       <c r="D34">
-        <v>5836.792087212412</v>
+        <v>5834.461165678741</v>
       </c>
       <c r="E34">
-        <v>-694.1959999999999</v>
+        <v>-630.3240000000001</v>
       </c>
       <c r="F34">
-        <v>2043.904</v>
+        <v>2107.776</v>
       </c>
       <c r="G34">
         <v>318.6</v>
@@ -4069,28 +4069,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M34">
-        <v>131.0142464</v>
+        <v>135.1084416</v>
       </c>
       <c r="N34">
-        <v>283.1190869333333</v>
+        <v>279.0248917333333</v>
       </c>
       <c r="O34">
-        <v>56.62381738666666</v>
+        <v>55.80497834666666</v>
       </c>
       <c r="P34">
-        <v>226.4952695466666</v>
+        <v>223.2199133866666</v>
       </c>
       <c r="Q34">
-        <v>558.0952695466666</v>
+        <v>554.8199133866666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07716820595071999</v>
+        <v>0.07756836165872766</v>
       </c>
       <c r="T34">
-        <v>0.6114247195905654</v>
+        <v>0.6192244991490623</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.160979395087626</v>
+        <v>3.065192140691032</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06889320231134753</v>
+        <v>0.07102402457620545</v>
       </c>
       <c r="C35">
-        <v>4045.285165678742</v>
+        <v>3488.541787532178</v>
       </c>
       <c r="D35">
-        <v>5834.461165678741</v>
+        <v>5341.589787532178</v>
       </c>
       <c r="E35">
-        <v>-630.3240000000001</v>
+        <v>-566.4519999999998</v>
       </c>
       <c r="F35">
-        <v>2107.776</v>
+        <v>2171.648</v>
       </c>
       <c r="G35">
         <v>318.6</v>
@@ -4151,45 +4151,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M35">
-        <v>135.1084416</v>
+        <v>156.1414912</v>
       </c>
       <c r="N35">
-        <v>279.0248917333333</v>
+        <v>257.9918421333333</v>
       </c>
       <c r="O35">
-        <v>55.80497834666666</v>
+        <v>51.59836842666665</v>
       </c>
       <c r="P35">
-        <v>223.2199133866666</v>
+        <v>206.3934737066666</v>
       </c>
       <c r="Q35">
-        <v>554.8199133866666</v>
+        <v>537.9934737066666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07756836165872766</v>
+        <v>0.07798064329728099</v>
       </c>
       <c r="T35">
-        <v>0.6192244991490623</v>
+        <v>0.6272606356638771</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.065192140691032</v>
+        <v>2.652295236522842</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07102402457620545</v>
+        <v>0.07109564684106338</v>
       </c>
       <c r="C36">
-        <v>3488.541787532178</v>
+        <v>3409.54557422667</v>
       </c>
       <c r="D36">
-        <v>5341.589787532178</v>
+        <v>5326.46557422667</v>
       </c>
       <c r="E36">
-        <v>-566.4519999999998</v>
+        <v>-502.5799999999999</v>
       </c>
       <c r="F36">
-        <v>2171.648</v>
+        <v>2235.52</v>
       </c>
       <c r="G36">
         <v>318.6</v>
@@ -4233,28 +4233,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M36">
-        <v>156.1414912</v>
+        <v>160.733888</v>
       </c>
       <c r="N36">
-        <v>257.9918421333333</v>
+        <v>253.3994453333333</v>
       </c>
       <c r="O36">
-        <v>51.59836842666665</v>
+        <v>50.67988906666665</v>
       </c>
       <c r="P36">
-        <v>206.3934737066666</v>
+        <v>202.7195562666666</v>
       </c>
       <c r="Q36">
-        <v>537.9934737066666</v>
+        <v>534.3195562666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07798064329728099</v>
+        <v>0.0784056105247129</v>
       </c>
       <c r="T36">
-        <v>0.6272606356638771</v>
+        <v>0.6355440379176095</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.652295236522842</v>
+        <v>2.57651537262219</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07109564684106338</v>
+        <v>0.07116726910592132</v>
       </c>
       <c r="C37">
-        <v>3409.54557422667</v>
+        <v>3330.634764707166</v>
       </c>
       <c r="D37">
-        <v>5326.46557422667</v>
+        <v>5311.426764707166</v>
       </c>
       <c r="E37">
-        <v>-502.5799999999999</v>
+        <v>-438.7079999999996</v>
       </c>
       <c r="F37">
-        <v>2235.52</v>
+        <v>2299.392</v>
       </c>
       <c r="G37">
         <v>318.6</v>
@@ -4315,28 +4315,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M37">
-        <v>160.733888</v>
+        <v>165.3262848</v>
       </c>
       <c r="N37">
-        <v>253.3994453333333</v>
+        <v>248.8070485333332</v>
       </c>
       <c r="O37">
-        <v>50.67988906666665</v>
+        <v>49.76140970666665</v>
       </c>
       <c r="P37">
-        <v>202.7195562666666</v>
+        <v>199.0456388266666</v>
       </c>
       <c r="Q37">
-        <v>534.3195562666666</v>
+        <v>530.6456388266665</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0784056105247129</v>
+        <v>0.07884385797800206</v>
       </c>
       <c r="T37">
-        <v>0.6355440379176095</v>
+        <v>0.644086296491771</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.57651537262219</v>
+        <v>2.504945501160462</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0711672691059213</v>
+        <v>0.07239329137077925</v>
       </c>
       <c r="C38">
-        <v>3330.63476470717</v>
+        <v>3021.89170377303</v>
       </c>
       <c r="D38">
-        <v>5311.426764707169</v>
+        <v>5066.55570377303</v>
       </c>
       <c r="E38">
-        <v>-438.7080000000001</v>
+        <v>-374.8359999999998</v>
       </c>
       <c r="F38">
-        <v>2299.392</v>
+        <v>2363.264</v>
       </c>
       <c r="G38">
         <v>318.6</v>
@@ -4397,45 +4397,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M38">
-        <v>165.3262848</v>
+        <v>179.1354112</v>
       </c>
       <c r="N38">
-        <v>248.8070485333333</v>
+        <v>234.9979221333332</v>
       </c>
       <c r="O38">
-        <v>49.76140970666665</v>
+        <v>46.99958442666665</v>
       </c>
       <c r="P38">
-        <v>199.0456388266666</v>
+        <v>187.9983377066666</v>
       </c>
       <c r="Q38">
-        <v>530.6456388266665</v>
+        <v>519.5983377066666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07884385797800204</v>
+        <v>0.07929601804885594</v>
       </c>
       <c r="T38">
-        <v>0.6440862964917708</v>
+        <v>0.6528997378778105</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.504945501160462</v>
+        <v>2.311845159810218</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07239329137077925</v>
+        <v>0.07249611363563717</v>
       </c>
       <c r="C39">
-        <v>3021.89170377303</v>
+        <v>2938.505450140422</v>
       </c>
       <c r="D39">
-        <v>5066.55570377303</v>
+        <v>5047.041450140422</v>
       </c>
       <c r="E39">
-        <v>-374.8359999999998</v>
+        <v>-310.9639999999999</v>
       </c>
       <c r="F39">
-        <v>2363.264</v>
+        <v>2427.136</v>
       </c>
       <c r="G39">
         <v>318.6</v>
@@ -4479,28 +4479,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M39">
-        <v>179.1354112</v>
+        <v>183.9769088</v>
       </c>
       <c r="N39">
-        <v>234.9979221333332</v>
+        <v>230.1564245333333</v>
       </c>
       <c r="O39">
-        <v>46.99958442666665</v>
+        <v>46.03128490666666</v>
       </c>
       <c r="P39">
-        <v>187.9983377066666</v>
+        <v>184.1251396266666</v>
       </c>
       <c r="Q39">
-        <v>519.5983377066666</v>
+        <v>515.7251396266665</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07929601804885594</v>
+        <v>0.07976276392844704</v>
       </c>
       <c r="T39">
-        <v>0.6528997378778105</v>
+        <v>0.6619974838246899</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.311845159810218</v>
+        <v>2.251007129288897</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07249611363563717</v>
+        <v>0.0725989359004951</v>
       </c>
       <c r="C40">
-        <v>2938.505450140422</v>
+        <v>2855.268941241183</v>
       </c>
       <c r="D40">
-        <v>5047.041450140422</v>
+        <v>5027.676941241182</v>
       </c>
       <c r="E40">
-        <v>-310.9639999999999</v>
+        <v>-247.0920000000001</v>
       </c>
       <c r="F40">
-        <v>2427.136</v>
+        <v>2491.008</v>
       </c>
       <c r="G40">
         <v>318.6</v>
@@ -4561,28 +4561,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M40">
-        <v>183.9769088</v>
+        <v>188.8184064</v>
       </c>
       <c r="N40">
-        <v>230.1564245333333</v>
+        <v>225.3149269333333</v>
       </c>
       <c r="O40">
-        <v>46.03128490666666</v>
+        <v>45.06298538666665</v>
       </c>
       <c r="P40">
-        <v>184.1251396266666</v>
+        <v>180.2519415466666</v>
       </c>
       <c r="Q40">
-        <v>515.7251396266665</v>
+        <v>511.8519415466666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07976276392844704</v>
+        <v>0.0802448129516313</v>
       </c>
       <c r="T40">
-        <v>0.6619974838246899</v>
+        <v>0.6713935165239262</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.251007129288897</v>
+        <v>2.193288997768669</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0725989359004951</v>
+        <v>0.07270175816535303</v>
       </c>
       <c r="C41">
-        <v>2855.268941241183</v>
+        <v>2772.18046003966</v>
       </c>
       <c r="D41">
-        <v>5027.676941241182</v>
+        <v>5008.46046003966</v>
       </c>
       <c r="E41">
-        <v>-247.0920000000001</v>
+        <v>-183.2199999999998</v>
       </c>
       <c r="F41">
-        <v>2491.008</v>
+        <v>2554.88</v>
       </c>
       <c r="G41">
         <v>318.6</v>
@@ -4643,28 +4643,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M41">
-        <v>188.8184064</v>
+        <v>193.659904</v>
       </c>
       <c r="N41">
-        <v>225.3149269333333</v>
+        <v>220.4734293333333</v>
       </c>
       <c r="O41">
-        <v>45.06298538666665</v>
+        <v>44.09468586666665</v>
       </c>
       <c r="P41">
-        <v>180.2519415466666</v>
+        <v>176.3787434666666</v>
       </c>
       <c r="Q41">
-        <v>511.8519415466666</v>
+        <v>507.9787434666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0802448129516313</v>
+        <v>0.08074293027558838</v>
       </c>
       <c r="T41">
-        <v>0.6713935165239262</v>
+        <v>0.6811027503131371</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.193288997768669</v>
+        <v>2.138456772824452</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07270175816535303</v>
+        <v>0.07280458043021096</v>
       </c>
       <c r="C42">
-        <v>2772.18046003966</v>
+        <v>2689.238315651246</v>
       </c>
       <c r="D42">
-        <v>5008.46046003966</v>
+        <v>4989.390315651246</v>
       </c>
       <c r="E42">
-        <v>-183.2199999999998</v>
+        <v>-119.348</v>
       </c>
       <c r="F42">
-        <v>2554.88</v>
+        <v>2618.752</v>
       </c>
       <c r="G42">
         <v>318.6</v>
@@ -4725,28 +4725,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M42">
-        <v>193.659904</v>
+        <v>198.5014016</v>
       </c>
       <c r="N42">
-        <v>220.4734293333333</v>
+        <v>215.6319317333333</v>
       </c>
       <c r="O42">
-        <v>44.09468586666665</v>
+        <v>43.12638634666666</v>
       </c>
       <c r="P42">
-        <v>176.3787434666666</v>
+        <v>172.5055453866666</v>
       </c>
       <c r="Q42">
-        <v>507.9787434666666</v>
+        <v>504.1055453866666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08074293027558838</v>
+        <v>0.08125793293256094</v>
       </c>
       <c r="T42">
-        <v>0.6811027503131371</v>
+        <v>0.6911411106714737</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.138456772824452</v>
+        <v>2.086299290560441</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07280458043021096</v>
+        <v>0.07290740269506889</v>
       </c>
       <c r="C43">
-        <v>2689.238315651246</v>
+        <v>2606.440842846402</v>
       </c>
       <c r="D43">
-        <v>4989.390315651246</v>
+        <v>4970.464842846402</v>
       </c>
       <c r="E43">
-        <v>-119.348</v>
+        <v>-55.47599999999966</v>
       </c>
       <c r="F43">
-        <v>2618.752</v>
+        <v>2682.624</v>
       </c>
       <c r="G43">
         <v>318.6</v>
@@ -4807,28 +4807,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M43">
-        <v>198.5014016</v>
+        <v>203.3428992</v>
       </c>
       <c r="N43">
-        <v>215.6319317333333</v>
+        <v>210.7904341333332</v>
       </c>
       <c r="O43">
-        <v>43.12638634666666</v>
+        <v>42.15808682666665</v>
       </c>
       <c r="P43">
-        <v>172.5055453866666</v>
+        <v>168.6323473066666</v>
       </c>
       <c r="Q43">
-        <v>504.1055453866666</v>
+        <v>500.2323473066666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08125793293256094</v>
+        <v>0.08179069430184291</v>
       </c>
       <c r="T43">
-        <v>0.6911411106714737</v>
+        <v>0.7015256213869943</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.086299290560441</v>
+        <v>2.03662549792805</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07290740269506889</v>
+        <v>0.07789502495992681</v>
       </c>
       <c r="C44">
-        <v>2606.440842846402</v>
+        <v>1770.15002878324</v>
       </c>
       <c r="D44">
-        <v>4970.464842846402</v>
+        <v>4198.04602878324</v>
       </c>
       <c r="E44">
-        <v>-55.47600000000011</v>
+        <v>8.396000000000186</v>
       </c>
       <c r="F44">
-        <v>2682.624</v>
+        <v>2746.496</v>
       </c>
       <c r="G44">
         <v>318.6</v>
@@ -4889,45 +4889,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M44">
-        <v>203.3428992</v>
+        <v>247.18464</v>
       </c>
       <c r="N44">
-        <v>210.7904341333333</v>
+        <v>166.9486933333333</v>
       </c>
       <c r="O44">
-        <v>42.15808682666665</v>
+        <v>33.38973866666665</v>
       </c>
       <c r="P44">
-        <v>168.6323473066666</v>
+        <v>133.5589546666666</v>
       </c>
       <c r="Q44">
-        <v>500.2323473066666</v>
+        <v>465.1589546666665</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0817906943018429</v>
+        <v>0.08234214905250317</v>
       </c>
       <c r="T44">
-        <v>0.7015256213869941</v>
+        <v>0.7122745008995507</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.03662549792805</v>
+        <v>1.675400758450579</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07789502495992681</v>
+        <v>0.07811144722478475</v>
       </c>
       <c r="C45">
-        <v>1770.15002878324</v>
+        <v>1678.15949162189</v>
       </c>
       <c r="D45">
-        <v>4198.04602878324</v>
+        <v>4169.927491621889</v>
       </c>
       <c r="E45">
-        <v>8.396000000000186</v>
+        <v>72.26800000000003</v>
       </c>
       <c r="F45">
-        <v>2746.496</v>
+        <v>2810.368</v>
       </c>
       <c r="G45">
         <v>318.6</v>
@@ -4971,28 +4971,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M45">
-        <v>247.18464</v>
+        <v>252.93312</v>
       </c>
       <c r="N45">
-        <v>166.9486933333333</v>
+        <v>161.2002133333333</v>
       </c>
       <c r="O45">
-        <v>33.38973866666665</v>
+        <v>32.24004266666666</v>
       </c>
       <c r="P45">
-        <v>133.5589546666666</v>
+        <v>128.9601706666666</v>
       </c>
       <c r="Q45">
-        <v>465.1589546666665</v>
+        <v>460.5601706666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08234214905250317</v>
+        <v>0.08291329861568703</v>
       </c>
       <c r="T45">
-        <v>0.7122745008995507</v>
+        <v>0.7234072689661268</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.675400758450579</v>
+        <v>1.637323468485793</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07811144722478475</v>
+        <v>0.07832786948964267</v>
       </c>
       <c r="C46">
-        <v>1678.15949162189</v>
+        <v>1586.543124524085</v>
       </c>
       <c r="D46">
-        <v>4169.927491621889</v>
+        <v>4142.183124524085</v>
       </c>
       <c r="E46">
-        <v>72.26800000000003</v>
+        <v>136.1399999999999</v>
       </c>
       <c r="F46">
-        <v>2810.368</v>
+        <v>2874.24</v>
       </c>
       <c r="G46">
         <v>318.6</v>
@@ -5053,28 +5053,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M46">
-        <v>252.93312</v>
+        <v>258.6815999999999</v>
       </c>
       <c r="N46">
-        <v>161.2002133333333</v>
+        <v>155.4517333333333</v>
       </c>
       <c r="O46">
-        <v>32.24004266666666</v>
+        <v>31.09034666666667</v>
       </c>
       <c r="P46">
-        <v>128.9601706666666</v>
+        <v>124.3613866666667</v>
       </c>
       <c r="Q46">
-        <v>460.5601706666666</v>
+        <v>455.9613866666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08291329861568703</v>
+        <v>0.08350521725389576</v>
       </c>
       <c r="T46">
-        <v>0.7234072689661268</v>
+        <v>0.7349448649623969</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.637323468485793</v>
+        <v>1.600938502519442</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07832786948964267</v>
+        <v>0.07854429175450059</v>
       </c>
       <c r="C47">
-        <v>1586.543124524085</v>
+        <v>1495.293508297509</v>
       </c>
       <c r="D47">
-        <v>4142.183124524085</v>
+        <v>4114.805508297509</v>
       </c>
       <c r="E47">
-        <v>136.1399999999999</v>
+        <v>200.0120000000002</v>
       </c>
       <c r="F47">
-        <v>2874.24</v>
+        <v>2938.112</v>
       </c>
       <c r="G47">
         <v>318.6</v>
@@ -5135,28 +5135,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M47">
-        <v>258.6815999999999</v>
+        <v>264.43008</v>
       </c>
       <c r="N47">
-        <v>155.4517333333333</v>
+        <v>149.7032533333333</v>
       </c>
       <c r="O47">
-        <v>31.09034666666667</v>
+        <v>29.94065066666666</v>
       </c>
       <c r="P47">
-        <v>124.3613866666667</v>
+        <v>119.7626026666666</v>
       </c>
       <c r="Q47">
-        <v>455.9613866666666</v>
+        <v>451.3626026666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08350521725389576</v>
+        <v>0.08411905880463073</v>
       </c>
       <c r="T47">
-        <v>0.7349448649623969</v>
+        <v>0.7469097793288991</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.600938502519442</v>
+        <v>1.566135491595106</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07854429175450059</v>
+        <v>0.07876071401935852</v>
       </c>
       <c r="C48">
-        <v>1495.293508297509</v>
+        <v>1404.403418609505</v>
       </c>
       <c r="D48">
-        <v>4114.805508297509</v>
+        <v>4087.787418609505</v>
       </c>
       <c r="E48">
-        <v>200.0120000000002</v>
+        <v>263.884</v>
       </c>
       <c r="F48">
-        <v>2938.112</v>
+        <v>3001.984</v>
       </c>
       <c r="G48">
         <v>318.6</v>
@@ -5217,28 +5217,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M48">
-        <v>264.43008</v>
+        <v>270.17856</v>
       </c>
       <c r="N48">
-        <v>149.7032533333333</v>
+        <v>143.9547733333333</v>
       </c>
       <c r="O48">
-        <v>29.94065066666666</v>
+        <v>28.79095466666665</v>
       </c>
       <c r="P48">
-        <v>119.7626026666666</v>
+        <v>115.1638186666666</v>
       </c>
       <c r="Q48">
-        <v>451.3626026666666</v>
+        <v>446.7638186666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08411905880463073</v>
+        <v>0.08475606418746891</v>
       </c>
       <c r="T48">
-        <v>0.7469097793288991</v>
+        <v>0.7593261998979107</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.566135491595106</v>
+        <v>1.53281345985904</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07876071401935852</v>
+        <v>0.07897713628421646</v>
       </c>
       <c r="C49">
-        <v>1404.403418609505</v>
+        <v>1313.86581963151</v>
       </c>
       <c r="D49">
-        <v>4087.787418609505</v>
+        <v>4061.121819631509</v>
       </c>
       <c r="E49">
-        <v>263.884</v>
+        <v>327.7560000000003</v>
       </c>
       <c r="F49">
-        <v>3001.984</v>
+        <v>3065.856</v>
       </c>
       <c r="G49">
         <v>318.6</v>
@@ -5299,28 +5299,28 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M49">
-        <v>270.17856</v>
+        <v>275.92704</v>
       </c>
       <c r="N49">
-        <v>143.9547733333333</v>
+        <v>138.2062933333332</v>
       </c>
       <c r="O49">
-        <v>28.79095466666665</v>
+        <v>27.64125866666665</v>
       </c>
       <c r="P49">
-        <v>115.1638186666666</v>
+        <v>110.5650346666666</v>
       </c>
       <c r="Q49">
-        <v>446.7638186666666</v>
+        <v>442.1650346666665</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08475606418746891</v>
+        <v>0.08541756977733933</v>
       </c>
       <c r="T49">
-        <v>0.7593261998979107</v>
+        <v>0.7722201751041922</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.53281345985904</v>
+        <v>1.500879846111977</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07897713628421645</v>
+        <v>0.1030982073781582</v>
       </c>
       <c r="C50">
-        <v>1313.865819631511</v>
+        <v>-459.6339787737684</v>
       </c>
       <c r="D50">
-        <v>4061.121819631511</v>
+        <v>2351.494021226232</v>
       </c>
       <c r="E50">
-        <v>327.7559999999999</v>
+        <v>391.6280000000002</v>
       </c>
       <c r="F50">
-        <v>3065.856</v>
+        <v>3129.728</v>
       </c>
       <c r="G50">
         <v>318.6</v>
@@ -5381,45 +5381,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M50">
-        <v>275.92704</v>
+        <v>459.4440704</v>
       </c>
       <c r="N50">
-        <v>138.2062933333333</v>
+        <v>-45.31073706666677</v>
       </c>
       <c r="O50">
-        <v>27.64125866666666</v>
+        <v>-9.062147413333355</v>
       </c>
       <c r="P50">
-        <v>110.5650346666666</v>
+        <v>-36.24858965333342</v>
       </c>
       <c r="Q50">
-        <v>442.1650346666666</v>
+        <v>295.3514103466666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08541756977733933</v>
+        <v>0.08653688087954046</v>
       </c>
       <c r="T50">
-        <v>0.7722201751041922</v>
+        <v>0.7940376318587513</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2</v>
+        <v>0.1802758420509298</v>
       </c>
       <c r="W50">
-        <v>0.07199999999999999</v>
+        <v>0.1203355063869235</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.500879846111977</v>
+        <v>0.9013792102546487</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1030982073781582</v>
+        <v>0.1041082073781582</v>
       </c>
       <c r="C51">
-        <v>-459.6339787737684</v>
+        <v>-564.2379626270072</v>
       </c>
       <c r="D51">
-        <v>2351.494021226232</v>
+        <v>2310.762037372993</v>
       </c>
       <c r="E51">
-        <v>391.6280000000002</v>
+        <v>455.5</v>
       </c>
       <c r="F51">
-        <v>3129.728</v>
+        <v>3193.6</v>
       </c>
       <c r="G51">
         <v>318.6</v>
@@ -5463,37 +5463,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M51">
-        <v>459.4440704</v>
+        <v>468.82048</v>
       </c>
       <c r="N51">
-        <v>-45.31073706666677</v>
+        <v>-54.68714666666676</v>
       </c>
       <c r="O51">
-        <v>-9.062147413333355</v>
+        <v>-10.93742933333335</v>
       </c>
       <c r="P51">
-        <v>-36.24858965333342</v>
+        <v>-43.74971733333341</v>
       </c>
       <c r="Q51">
-        <v>295.3514103466666</v>
+        <v>287.8502826666665</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08653688087954046</v>
+        <v>0.08735161849713127</v>
       </c>
       <c r="T51">
-        <v>0.7940376318587513</v>
+        <v>0.8099183844959265</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1802758420509298</v>
+        <v>0.1766703252099112</v>
       </c>
       <c r="W51">
-        <v>0.1203355063869235</v>
+        <v>0.1208647962591851</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9013792102546487</v>
+        <v>0.8833516260495557</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1041082073781582</v>
+        <v>0.1051182073781582</v>
       </c>
       <c r="C52">
-        <v>-564.2379626270072</v>
+        <v>-667.4548747695494</v>
       </c>
       <c r="D52">
-        <v>2310.762037372993</v>
+        <v>2271.41712523045</v>
       </c>
       <c r="E52">
-        <v>455.5</v>
+        <v>519.3719999999998</v>
       </c>
       <c r="F52">
-        <v>3193.6</v>
+        <v>3257.472</v>
       </c>
       <c r="G52">
         <v>318.6</v>
@@ -5545,37 +5545,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M52">
-        <v>468.82048</v>
+        <v>478.1968896</v>
       </c>
       <c r="N52">
-        <v>-54.68714666666676</v>
+        <v>-64.06355626666675</v>
       </c>
       <c r="O52">
-        <v>-10.93742933333335</v>
+        <v>-12.81271125333335</v>
       </c>
       <c r="P52">
-        <v>-43.74971733333341</v>
+        <v>-51.2508450133334</v>
       </c>
       <c r="Q52">
-        <v>287.8502826666665</v>
+        <v>280.3491549866666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08735161849713127</v>
+        <v>0.08819961071135846</v>
       </c>
       <c r="T52">
-        <v>0.8099183844959265</v>
+        <v>0.8264473311182923</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1766703252099112</v>
+        <v>0.1732062011861874</v>
       </c>
       <c r="W52">
-        <v>0.1208647962591851</v>
+        <v>0.1213733296658677</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8833516260495557</v>
+        <v>0.8660310059309371</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1051182073781582</v>
+        <v>0.1061282073781582</v>
       </c>
       <c r="C53">
-        <v>-667.4548747695494</v>
+        <v>-769.3543812409807</v>
       </c>
       <c r="D53">
-        <v>2271.41712523045</v>
+        <v>2233.389618759019</v>
       </c>
       <c r="E53">
-        <v>519.3719999999998</v>
+        <v>583.2440000000001</v>
       </c>
       <c r="F53">
-        <v>3257.472</v>
+        <v>3321.344</v>
       </c>
       <c r="G53">
         <v>318.6</v>
@@ -5627,37 +5627,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M53">
-        <v>478.1968896</v>
+        <v>487.5732992000001</v>
       </c>
       <c r="N53">
-        <v>-64.06355626666675</v>
+        <v>-73.4399658666668</v>
       </c>
       <c r="O53">
-        <v>-12.81271125333335</v>
+        <v>-14.68799317333336</v>
       </c>
       <c r="P53">
-        <v>-51.2508450133334</v>
+        <v>-58.75197269333344</v>
       </c>
       <c r="Q53">
-        <v>280.3491549866666</v>
+        <v>272.8480273066666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08819961071135846</v>
+        <v>0.08908293593451175</v>
       </c>
       <c r="T53">
-        <v>0.8264473311182923</v>
+        <v>0.8436649838499234</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1732062011861874</v>
+        <v>0.1698753127018376</v>
       </c>
       <c r="W53">
-        <v>0.1213733296658677</v>
+        <v>0.1218623040953702</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8660310059309371</v>
+        <v>0.8493765635091882</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1061282073781582</v>
+        <v>0.1071382073781582</v>
       </c>
       <c r="C54">
-        <v>-769.3543812409807</v>
+        <v>-870.0015595737905</v>
       </c>
       <c r="D54">
-        <v>2233.389618759019</v>
+        <v>2196.61444042621</v>
       </c>
       <c r="E54">
-        <v>583.2440000000001</v>
+        <v>647.116</v>
       </c>
       <c r="F54">
-        <v>3321.344</v>
+        <v>3385.216</v>
       </c>
       <c r="G54">
         <v>318.6</v>
@@ -5709,37 +5709,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M54">
-        <v>487.5732992000001</v>
+        <v>496.9497088000001</v>
       </c>
       <c r="N54">
-        <v>-73.4399658666668</v>
+        <v>-82.81637546666678</v>
       </c>
       <c r="O54">
-        <v>-14.68799317333336</v>
+        <v>-16.56327509333336</v>
       </c>
       <c r="P54">
-        <v>-58.75197269333344</v>
+        <v>-66.25310037333342</v>
       </c>
       <c r="Q54">
-        <v>272.8480273066666</v>
+        <v>265.3468996266665</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08908293593451175</v>
+        <v>0.09000384946503329</v>
       </c>
       <c r="T54">
-        <v>0.8436649838499234</v>
+        <v>0.8616153026552409</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1698753127018376</v>
+        <v>0.1666701181225577</v>
       </c>
       <c r="W54">
-        <v>0.1218623040953702</v>
+        <v>0.1223328266596085</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8493765635091882</v>
+        <v>0.8333505906127885</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1071382073781582</v>
+        <v>0.1081482073781582</v>
       </c>
       <c r="C55">
-        <v>-870.0015595737905</v>
+        <v>-969.4572704473717</v>
       </c>
       <c r="D55">
-        <v>2196.61444042621</v>
+        <v>2161.030729552629</v>
       </c>
       <c r="E55">
-        <v>647.116</v>
+        <v>710.9880000000003</v>
       </c>
       <c r="F55">
-        <v>3385.216</v>
+        <v>3449.088</v>
       </c>
       <c r="G55">
         <v>318.6</v>
@@ -5791,37 +5791,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M55">
-        <v>496.9497088000001</v>
+        <v>506.3261184000001</v>
       </c>
       <c r="N55">
-        <v>-82.81637546666678</v>
+        <v>-92.19278506666683</v>
       </c>
       <c r="O55">
-        <v>-16.56327509333336</v>
+        <v>-18.43855701333337</v>
       </c>
       <c r="P55">
-        <v>-66.25310037333342</v>
+        <v>-73.75422805333346</v>
       </c>
       <c r="Q55">
-        <v>265.3468996266665</v>
+        <v>257.8457719466665</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09000384946503329</v>
+        <v>0.09096480271427312</v>
       </c>
       <c r="T55">
-        <v>0.8616153026552409</v>
+        <v>0.8803460701042679</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1666701181225577</v>
+        <v>0.1635836344536215</v>
       </c>
       <c r="W55">
-        <v>0.1223328266596085</v>
+        <v>0.1227859224622084</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8333505906127885</v>
+        <v>0.817918172268107</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1081482073781582</v>
+        <v>0.1091582073781582</v>
       </c>
       <c r="C56">
-        <v>-969.4572704473717</v>
+        <v>-1067.778493794569</v>
       </c>
       <c r="D56">
-        <v>2161.030729552629</v>
+        <v>2126.581506205431</v>
       </c>
       <c r="E56">
-        <v>710.9880000000003</v>
+        <v>774.8600000000001</v>
       </c>
       <c r="F56">
-        <v>3449.088</v>
+        <v>3512.96</v>
       </c>
       <c r="G56">
         <v>318.6</v>
@@ -5873,37 +5873,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M56">
-        <v>506.3261184000001</v>
+        <v>515.702528</v>
       </c>
       <c r="N56">
-        <v>-92.19278506666683</v>
+        <v>-101.5691946666668</v>
       </c>
       <c r="O56">
-        <v>-18.43855701333337</v>
+        <v>-20.31383893333335</v>
       </c>
       <c r="P56">
-        <v>-73.75422805333346</v>
+        <v>-81.2553557333334</v>
       </c>
       <c r="Q56">
-        <v>257.8457719466665</v>
+        <v>250.3446442666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09096480271427312</v>
+        <v>0.09196846499681255</v>
       </c>
       <c r="T56">
-        <v>0.8803460701042679</v>
+        <v>0.8999093161065851</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1635836344536215</v>
+        <v>0.1606093865544647</v>
       </c>
       <c r="W56">
-        <v>0.1227859224622084</v>
+        <v>0.1232225420538046</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.817918172268107</v>
+        <v>0.8030469327723234</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1091582073781582</v>
+        <v>0.1409495676840017</v>
       </c>
       <c r="C57">
-        <v>-1067.778493794569</v>
+        <v>-1842.183610540276</v>
       </c>
       <c r="D57">
-        <v>2126.581506205431</v>
+        <v>1416.048389459724</v>
       </c>
       <c r="E57">
-        <v>774.8600000000001</v>
+        <v>838.7320000000004</v>
       </c>
       <c r="F57">
-        <v>3512.96</v>
+        <v>3576.832</v>
       </c>
       <c r="G57">
         <v>318.6</v>
@@ -5955,45 +5955,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M57">
-        <v>515.702528</v>
+        <v>718.2278656000001</v>
       </c>
       <c r="N57">
-        <v>-101.5691946666668</v>
+        <v>-304.0945322666668</v>
       </c>
       <c r="O57">
-        <v>-20.31383893333335</v>
+        <v>-60.81890645333337</v>
       </c>
       <c r="P57">
-        <v>-81.2553557333334</v>
+        <v>-243.2756258133334</v>
       </c>
       <c r="Q57">
-        <v>250.3446442666666</v>
+        <v>88.32437418666652</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09196846499681255</v>
+        <v>0.09424811262365734</v>
       </c>
       <c r="T57">
-        <v>0.8999093161065851</v>
+        <v>0.9443438914596869</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1606093865544647</v>
+        <v>0.1153208760529976</v>
       </c>
       <c r="W57">
-        <v>0.1232225420538046</v>
+        <v>0.1776435680885581</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8030469327723234</v>
+        <v>0.5766043802649882</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1409495676840017</v>
+        <v>0.1424995676840018</v>
       </c>
       <c r="C58">
-        <v>-1842.183610540276</v>
+        <v>-1928.753488682142</v>
       </c>
       <c r="D58">
-        <v>1416.048389459724</v>
+        <v>1393.350511317858</v>
       </c>
       <c r="E58">
-        <v>838.7320000000004</v>
+        <v>902.6040000000003</v>
       </c>
       <c r="F58">
-        <v>3576.832</v>
+        <v>3640.704</v>
       </c>
       <c r="G58">
         <v>318.6</v>
@@ -6037,37 +6037,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M58">
-        <v>718.2278656000001</v>
+        <v>731.0533632</v>
       </c>
       <c r="N58">
-        <v>-304.0945322666668</v>
+        <v>-316.9200298666668</v>
       </c>
       <c r="O58">
-        <v>-60.81890645333337</v>
+        <v>-63.38400597333336</v>
       </c>
       <c r="P58">
-        <v>-243.2756258133334</v>
+        <v>-253.5360238933334</v>
       </c>
       <c r="Q58">
-        <v>88.32437418666652</v>
+        <v>78.06397610666656</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09424811262365734</v>
+        <v>0.09537481291723079</v>
       </c>
       <c r="T58">
-        <v>0.9443438914596869</v>
+        <v>0.9663053773075868</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1153208760529976</v>
+        <v>0.11329770278891</v>
       </c>
       <c r="W58">
-        <v>0.1776435680885581</v>
+        <v>0.1780498212799869</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5766043802649882</v>
+        <v>0.5664885139445499</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1424995676840018</v>
+        <v>0.1440495676840018</v>
       </c>
       <c r="C59">
-        <v>-1928.753488682142</v>
+        <v>-2014.607196525264</v>
       </c>
       <c r="D59">
-        <v>1393.350511317858</v>
+        <v>1371.368803474737</v>
       </c>
       <c r="E59">
-        <v>902.6040000000003</v>
+        <v>966.4760000000006</v>
       </c>
       <c r="F59">
-        <v>3640.704</v>
+        <v>3704.576</v>
       </c>
       <c r="G59">
         <v>318.6</v>
@@ -6119,37 +6119,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M59">
-        <v>731.0533632</v>
+        <v>743.8788608000001</v>
       </c>
       <c r="N59">
-        <v>-316.9200298666668</v>
+        <v>-329.7455274666668</v>
       </c>
       <c r="O59">
-        <v>-63.38400597333336</v>
+        <v>-65.94910549333336</v>
       </c>
       <c r="P59">
-        <v>-253.5360238933334</v>
+        <v>-263.7964219733335</v>
       </c>
       <c r="Q59">
-        <v>78.06397610666656</v>
+        <v>67.80357802666651</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09537481291723079</v>
+        <v>0.09655516560573629</v>
       </c>
       <c r="T59">
-        <v>0.9663053773075868</v>
+        <v>0.9893126481958627</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.11329770278891</v>
+        <v>0.1113442941201356</v>
       </c>
       <c r="W59">
-        <v>0.1780498212799869</v>
+        <v>0.1784420657406768</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5664885139445499</v>
+        <v>0.5567214706006782</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1440495676840017</v>
+        <v>0.1455995676840017</v>
       </c>
       <c r="C60">
-        <v>-2014.607196525262</v>
+        <v>-2099.778102870391</v>
       </c>
       <c r="D60">
-        <v>1371.368803474737</v>
+        <v>1350.069897129609</v>
       </c>
       <c r="E60">
-        <v>966.4759999999997</v>
+        <v>1030.348</v>
       </c>
       <c r="F60">
-        <v>3704.576</v>
+        <v>3768.448</v>
       </c>
       <c r="G60">
         <v>318.6</v>
@@ -6201,37 +6201,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M60">
-        <v>743.8788608</v>
+        <v>756.7043584</v>
       </c>
       <c r="N60">
-        <v>-329.7455274666667</v>
+        <v>-342.5710250666668</v>
       </c>
       <c r="O60">
-        <v>-65.94910549333335</v>
+        <v>-68.51420501333335</v>
       </c>
       <c r="P60">
-        <v>-263.7964219733334</v>
+        <v>-274.0568200533334</v>
       </c>
       <c r="Q60">
-        <v>67.80357802666657</v>
+        <v>57.54317994666656</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09655516560573627</v>
+        <v>0.09779309647416885</v>
       </c>
       <c r="T60">
-        <v>0.9893126481958623</v>
+        <v>1.013442224981127</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1113442941201357</v>
+        <v>0.1094571026943706</v>
       </c>
       <c r="W60">
-        <v>0.1784420657406768</v>
+        <v>0.1788210137789704</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5567214706006783</v>
+        <v>0.5472855134718533</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1455995676840017</v>
+        <v>0.1471495676840018</v>
       </c>
       <c r="C61">
-        <v>-2099.778102870391</v>
+        <v>-2184.297535201582</v>
       </c>
       <c r="D61">
-        <v>1350.069897129609</v>
+        <v>1329.422464798417</v>
       </c>
       <c r="E61">
-        <v>1030.348</v>
+        <v>1094.22</v>
       </c>
       <c r="F61">
-        <v>3768.448</v>
+        <v>3832.32</v>
       </c>
       <c r="G61">
         <v>318.6</v>
@@ -6283,37 +6283,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M61">
-        <v>756.7043584</v>
+        <v>769.529856</v>
       </c>
       <c r="N61">
-        <v>-342.5710250666668</v>
+        <v>-355.3965226666667</v>
       </c>
       <c r="O61">
-        <v>-68.51420501333335</v>
+        <v>-71.07930453333334</v>
       </c>
       <c r="P61">
-        <v>-274.0568200533334</v>
+        <v>-284.3172181333334</v>
       </c>
       <c r="Q61">
-        <v>57.54317994666656</v>
+        <v>47.2827818666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09779309647416885</v>
+        <v>0.09909292388602309</v>
       </c>
       <c r="T61">
-        <v>1.013442224981127</v>
+        <v>1.038778280605656</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1094571026943706</v>
+        <v>0.1076328176494645</v>
       </c>
       <c r="W61">
-        <v>0.1788210137789704</v>
+        <v>0.1791873302159875</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5472855134718533</v>
+        <v>0.5381640882473224</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1471495676840018</v>
+        <v>0.1486995676840017</v>
       </c>
       <c r="C62">
-        <v>-2184.297535201582</v>
+        <v>-2268.194933430324</v>
       </c>
       <c r="D62">
-        <v>1329.422464798417</v>
+        <v>1309.397066569675</v>
       </c>
       <c r="E62">
-        <v>1094.22</v>
+        <v>1158.092</v>
       </c>
       <c r="F62">
-        <v>3832.32</v>
+        <v>3896.192</v>
       </c>
       <c r="G62">
         <v>318.6</v>
@@ -6365,37 +6365,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M62">
-        <v>769.529856</v>
+        <v>782.3553536000001</v>
       </c>
       <c r="N62">
-        <v>-355.3965226666667</v>
+        <v>-368.2220202666668</v>
       </c>
       <c r="O62">
-        <v>-71.07930453333334</v>
+        <v>-73.64440405333336</v>
       </c>
       <c r="P62">
-        <v>-284.3172181333334</v>
+        <v>-294.5776162133334</v>
       </c>
       <c r="Q62">
-        <v>47.2827818666666</v>
+        <v>37.02238378666652</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09909292388602309</v>
+        <v>0.1004594091138698</v>
       </c>
       <c r="T62">
-        <v>1.038778280605656</v>
+        <v>1.065413621134006</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1076328176494645</v>
+        <v>0.1058683452289814</v>
       </c>
       <c r="W62">
-        <v>0.1791873302159875</v>
+        <v>0.1795416362780205</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5381640882473224</v>
+        <v>0.5293417261449072</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1486995676840017</v>
+        <v>0.1502495676840018</v>
       </c>
       <c r="C63">
-        <v>-2268.194933430324</v>
+        <v>-2351.497989950569</v>
       </c>
       <c r="D63">
-        <v>1309.397066569675</v>
+        <v>1289.966010049431</v>
       </c>
       <c r="E63">
-        <v>1158.092</v>
+        <v>1221.964</v>
       </c>
       <c r="F63">
-        <v>3896.192</v>
+        <v>3960.064</v>
       </c>
       <c r="G63">
         <v>318.6</v>
@@ -6447,37 +6447,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M63">
-        <v>782.3553536000001</v>
+        <v>795.1808512</v>
       </c>
       <c r="N63">
-        <v>-368.2220202666668</v>
+        <v>-381.0475178666667</v>
       </c>
       <c r="O63">
-        <v>-73.64440405333336</v>
+        <v>-76.20950357333335</v>
       </c>
       <c r="P63">
-        <v>-294.5776162133334</v>
+        <v>-304.8380142933334</v>
       </c>
       <c r="Q63">
-        <v>37.02238378666652</v>
+        <v>26.76198570666656</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1004594091138698</v>
+        <v>0.1018978146168664</v>
       </c>
       <c r="T63">
-        <v>1.065413621134006</v>
+        <v>1.093450821690164</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1058683452289814</v>
+        <v>0.1041607912736753</v>
       </c>
       <c r="W63">
-        <v>0.1795416362780205</v>
+        <v>0.179884513112246</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5293417261449072</v>
+        <v>0.5208039563683764</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1502495676840018</v>
+        <v>0.1517995676840017</v>
       </c>
       <c r="C64">
-        <v>-2351.497989950569</v>
+        <v>-2434.232777405865</v>
       </c>
       <c r="D64">
-        <v>1289.966010049431</v>
+        <v>1271.103222594135</v>
       </c>
       <c r="E64">
-        <v>1221.964</v>
+        <v>1285.836</v>
       </c>
       <c r="F64">
-        <v>3960.064</v>
+        <v>4023.936</v>
       </c>
       <c r="G64">
         <v>318.6</v>
@@ -6529,37 +6529,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M64">
-        <v>795.1808512</v>
+        <v>808.0063488</v>
       </c>
       <c r="N64">
-        <v>-381.0475178666667</v>
+        <v>-393.8730154666667</v>
       </c>
       <c r="O64">
-        <v>-76.20950357333335</v>
+        <v>-78.77460309333334</v>
       </c>
       <c r="P64">
-        <v>-304.8380142933334</v>
+        <v>-315.0984123733334</v>
       </c>
       <c r="Q64">
-        <v>26.76198570666656</v>
+        <v>16.50158762666661</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1018978146168664</v>
+        <v>0.1034139717686736</v>
       </c>
       <c r="T64">
-        <v>1.093450821690164</v>
+        <v>1.123003546600709</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1041607912736753</v>
+        <v>0.1025074453804424</v>
       </c>
       <c r="W64">
-        <v>0.179884513112246</v>
+        <v>0.1802165049676072</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5208039563683764</v>
+        <v>0.5125372269022118</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1517995676840017</v>
+        <v>0.1533495676840018</v>
       </c>
       <c r="C65">
-        <v>-2434.232777405865</v>
+        <v>-2516.423865408243</v>
       </c>
       <c r="D65">
-        <v>1271.103222594135</v>
+        <v>1252.784134591757</v>
       </c>
       <c r="E65">
-        <v>1285.836</v>
+        <v>1349.708</v>
       </c>
       <c r="F65">
-        <v>4023.936</v>
+        <v>4087.808</v>
       </c>
       <c r="G65">
         <v>318.6</v>
@@ -6611,37 +6611,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M65">
-        <v>808.0063488</v>
+        <v>820.8318464</v>
       </c>
       <c r="N65">
-        <v>-393.8730154666667</v>
+        <v>-406.6985130666667</v>
       </c>
       <c r="O65">
-        <v>-78.77460309333334</v>
+        <v>-81.33970261333336</v>
       </c>
       <c r="P65">
-        <v>-315.0984123733334</v>
+        <v>-325.3588104533334</v>
       </c>
       <c r="Q65">
-        <v>16.50158762666661</v>
+        <v>6.24118954666659</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1034139717686736</v>
+        <v>0.105014359873359</v>
       </c>
       <c r="T65">
-        <v>1.123003546600709</v>
+        <v>1.15419808956184</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1025074453804424</v>
+        <v>0.1009057665463729</v>
       </c>
       <c r="W65">
-        <v>0.1802165049676072</v>
+        <v>0.1805381220774883</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5125372269022118</v>
+        <v>0.5045288327318647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1533495676840018</v>
+        <v>0.177868013106317</v>
       </c>
       <c r="C66">
-        <v>-2516.423865408243</v>
+        <v>-2812.875418227012</v>
       </c>
       <c r="D66">
-        <v>1252.784134591757</v>
+        <v>1020.204581772988</v>
       </c>
       <c r="E66">
-        <v>1349.708</v>
+        <v>1413.58</v>
       </c>
       <c r="F66">
-        <v>4087.808</v>
+        <v>4151.68</v>
       </c>
       <c r="G66">
         <v>318.6</v>
@@ -6693,45 +6693,45 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M66">
-        <v>820.8318464</v>
+        <v>978.9661440000001</v>
       </c>
       <c r="N66">
-        <v>-406.6985130666667</v>
+        <v>-564.8328106666668</v>
       </c>
       <c r="O66">
-        <v>-81.33970261333336</v>
+        <v>-112.9665621333334</v>
       </c>
       <c r="P66">
-        <v>-325.3588104533334</v>
+        <v>-451.8662485333334</v>
       </c>
       <c r="Q66">
-        <v>6.24118954666659</v>
+        <v>-120.2662485333335</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.105014359873359</v>
+        <v>0.1073303285049271</v>
       </c>
       <c r="T66">
-        <v>1.15419808956184</v>
+        <v>1.199340628901249</v>
       </c>
       <c r="U66">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1009057665463729</v>
+        <v>0.08460626261112729</v>
       </c>
       <c r="W66">
-        <v>0.1805381220774883</v>
+        <v>0.2158498432762962</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5045288327318647</v>
+        <v>0.4230313130556365</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.177868013106317</v>
+        <v>0.179768013106317</v>
       </c>
       <c r="C67">
-        <v>-2812.875418227012</v>
+        <v>-2891.216459458744</v>
       </c>
       <c r="D67">
-        <v>1020.204581772988</v>
+        <v>1005.735540541255</v>
       </c>
       <c r="E67">
-        <v>1413.58</v>
+        <v>1477.452</v>
       </c>
       <c r="F67">
-        <v>4151.68</v>
+        <v>4215.552</v>
       </c>
       <c r="G67">
         <v>318.6</v>
@@ -6775,37 +6775,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M67">
-        <v>978.9661440000001</v>
+        <v>994.0271616</v>
       </c>
       <c r="N67">
-        <v>-564.8328106666668</v>
+        <v>-579.8938282666668</v>
       </c>
       <c r="O67">
-        <v>-112.9665621333334</v>
+        <v>-115.9787656533334</v>
       </c>
       <c r="P67">
-        <v>-451.8662485333334</v>
+        <v>-463.9150626133334</v>
       </c>
       <c r="Q67">
-        <v>-120.2662485333335</v>
+        <v>-132.3150626133335</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1073303285049271</v>
+        <v>0.1091400440491896</v>
       </c>
       <c r="T67">
-        <v>1.199340628901249</v>
+        <v>1.234615353280697</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08460626261112729</v>
+        <v>0.08332434954126172</v>
       </c>
       <c r="W67">
-        <v>0.2158498432762962</v>
+        <v>0.2161521183781705</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4230313130556365</v>
+        <v>0.4166217477063086</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.179768013106317</v>
+        <v>0.181668013106317</v>
       </c>
       <c r="C68">
-        <v>-2891.216459458744</v>
+        <v>-2969.152825922492</v>
       </c>
       <c r="D68">
-        <v>1005.735540541255</v>
+        <v>991.6711740775081</v>
       </c>
       <c r="E68">
-        <v>1477.452</v>
+        <v>1541.324</v>
       </c>
       <c r="F68">
-        <v>4215.552</v>
+        <v>4279.424</v>
       </c>
       <c r="G68">
         <v>318.6</v>
@@ -6857,37 +6857,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M68">
-        <v>994.0271616</v>
+        <v>1009.0881792</v>
       </c>
       <c r="N68">
-        <v>-579.8938282666668</v>
+        <v>-594.9548458666668</v>
       </c>
       <c r="O68">
-        <v>-115.9787656533334</v>
+        <v>-118.9909691733334</v>
       </c>
       <c r="P68">
-        <v>-463.9150626133334</v>
+        <v>-475.9638766933334</v>
       </c>
       <c r="Q68">
-        <v>-132.3150626133335</v>
+        <v>-144.3638766933335</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1091400440491896</v>
+        <v>0.1110594393234075</v>
       </c>
       <c r="T68">
-        <v>1.234615353280697</v>
+        <v>1.272027939743749</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08332434954126172</v>
+        <v>0.0820807025331832</v>
       </c>
       <c r="W68">
-        <v>0.2161521183781705</v>
+        <v>0.2164453703426754</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4166217477063086</v>
+        <v>0.4104035126659159</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.181668013106317</v>
+        <v>0.183568013106317</v>
       </c>
       <c r="C69">
-        <v>-2969.152825922492</v>
+        <v>-3046.701260591642</v>
       </c>
       <c r="D69">
-        <v>991.6711740775081</v>
+        <v>977.9947394083576</v>
       </c>
       <c r="E69">
-        <v>1541.324</v>
+        <v>1605.196</v>
       </c>
       <c r="F69">
-        <v>4279.424</v>
+        <v>4343.296</v>
       </c>
       <c r="G69">
         <v>318.6</v>
@@ -6939,37 +6939,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M69">
-        <v>1009.0881792</v>
+        <v>1024.1491968</v>
       </c>
       <c r="N69">
-        <v>-594.9548458666668</v>
+        <v>-610.0158634666668</v>
       </c>
       <c r="O69">
-        <v>-118.9909691733334</v>
+        <v>-122.0031726933334</v>
       </c>
       <c r="P69">
-        <v>-475.9638766933334</v>
+        <v>-488.0126907733335</v>
       </c>
       <c r="Q69">
-        <v>-144.3638766933335</v>
+        <v>-156.4126907733335</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1110594393234075</v>
+        <v>0.113098796802264</v>
       </c>
       <c r="T69">
-        <v>1.272027939743749</v>
+        <v>1.311778812860741</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0820807025331832</v>
+        <v>0.08087363337828345</v>
       </c>
       <c r="W69">
-        <v>0.2164453703426754</v>
+        <v>0.2167299972494008</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4104035126659159</v>
+        <v>0.4043681668914171</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.183568013106317</v>
+        <v>0.185468013106317</v>
       </c>
       <c r="C70">
-        <v>-3046.701260591642</v>
+        <v>-3123.87759537488</v>
       </c>
       <c r="D70">
-        <v>977.9947394083576</v>
+        <v>964.6904046251209</v>
       </c>
       <c r="E70">
-        <v>1605.196</v>
+        <v>1669.068000000001</v>
       </c>
       <c r="F70">
-        <v>4343.296</v>
+        <v>4407.168000000001</v>
       </c>
       <c r="G70">
         <v>318.6</v>
@@ -7021,37 +7021,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M70">
-        <v>1024.1491968</v>
+        <v>1039.2102144</v>
       </c>
       <c r="N70">
-        <v>-610.0158634666668</v>
+        <v>-625.0768810666671</v>
       </c>
       <c r="O70">
-        <v>-122.0031726933334</v>
+        <v>-125.0153762133334</v>
       </c>
       <c r="P70">
-        <v>-488.0126907733335</v>
+        <v>-500.0615048533336</v>
       </c>
       <c r="Q70">
-        <v>-156.4126907733335</v>
+        <v>-168.4615048533337</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.113098796802264</v>
+        <v>0.1152697257313693</v>
       </c>
       <c r="T70">
-        <v>1.311778812860741</v>
+        <v>1.354094258436894</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08087363337828345</v>
+        <v>0.07970155173511989</v>
       </c>
       <c r="W70">
-        <v>0.2167299972494008</v>
+        <v>0.2170063741008587</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4043681668914171</v>
+        <v>0.3985077586755994</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.185468013106317</v>
+        <v>0.187368013106317</v>
       </c>
       <c r="C71">
-        <v>-3123.87759537488</v>
+        <v>-3200.696812253675</v>
       </c>
       <c r="D71">
-        <v>964.6904046251209</v>
+        <v>951.7431877463251</v>
       </c>
       <c r="E71">
-        <v>1669.068000000001</v>
+        <v>1732.94</v>
       </c>
       <c r="F71">
-        <v>4407.168000000001</v>
+        <v>4471.04</v>
       </c>
       <c r="G71">
         <v>318.6</v>
@@ -7103,37 +7103,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M71">
-        <v>1039.2102144</v>
+        <v>1054.271232</v>
       </c>
       <c r="N71">
-        <v>-625.0768810666671</v>
+        <v>-640.1378986666668</v>
       </c>
       <c r="O71">
-        <v>-125.0153762133334</v>
+        <v>-128.0275797333334</v>
       </c>
       <c r="P71">
-        <v>-500.0615048533336</v>
+        <v>-512.1103189333335</v>
       </c>
       <c r="Q71">
-        <v>-168.4615048533337</v>
+        <v>-180.5103189333335</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1152697257313693</v>
+        <v>0.1175853832557482</v>
       </c>
       <c r="T71">
-        <v>1.354094258436894</v>
+        <v>1.399230733718124</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07970155173511989</v>
+        <v>0.0785629581389039</v>
       </c>
       <c r="W71">
-        <v>0.2170063741008587</v>
+        <v>0.2172748544708465</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3985077586755994</v>
+        <v>0.3928147906945195</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.187368013106317</v>
+        <v>0.189268013106317</v>
       </c>
       <c r="C72">
-        <v>-3200.696812253675</v>
+        <v>-3277.173099561802</v>
       </c>
       <c r="D72">
-        <v>951.7431877463251</v>
+        <v>939.1389004381987</v>
       </c>
       <c r="E72">
-        <v>1732.94</v>
+        <v>1796.812</v>
       </c>
       <c r="F72">
-        <v>4471.04</v>
+        <v>4534.912</v>
       </c>
       <c r="G72">
         <v>318.6</v>
@@ -7185,37 +7185,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M72">
-        <v>1054.271232</v>
+        <v>1069.3322496</v>
       </c>
       <c r="N72">
-        <v>-640.1378986666668</v>
+        <v>-655.1989162666669</v>
       </c>
       <c r="O72">
-        <v>-128.0275797333334</v>
+        <v>-131.0397832533334</v>
       </c>
       <c r="P72">
-        <v>-512.1103189333335</v>
+        <v>-524.1591330133335</v>
       </c>
       <c r="Q72">
-        <v>-180.5103189333335</v>
+        <v>-192.5591330133336</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1175853832557482</v>
+        <v>0.1200607412990499</v>
       </c>
       <c r="T72">
-        <v>1.399230733718124</v>
+        <v>1.447480069363576</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0785629581389039</v>
+        <v>0.07745643760173626</v>
       </c>
       <c r="W72">
-        <v>0.2172748544708465</v>
+        <v>0.2175357720135106</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3928147906945195</v>
+        <v>0.3872821880086812</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.189268013106317</v>
+        <v>0.191168013106317</v>
       </c>
       <c r="C73">
-        <v>-3277.1730995618</v>
+        <v>-3353.319903851294</v>
       </c>
       <c r="D73">
-        <v>939.1389004381994</v>
+        <v>926.8640961487057</v>
       </c>
       <c r="E73">
-        <v>1796.811999999999</v>
+        <v>1860.684</v>
       </c>
       <c r="F73">
-        <v>4534.911999999999</v>
+        <v>4598.784</v>
       </c>
       <c r="G73">
         <v>318.6</v>
@@ -7267,37 +7267,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M73">
-        <v>1069.3322496</v>
+        <v>1084.3932672</v>
       </c>
       <c r="N73">
-        <v>-655.1989162666666</v>
+        <v>-670.2599338666666</v>
       </c>
       <c r="O73">
-        <v>-131.0397832533333</v>
+        <v>-134.0519867733333</v>
       </c>
       <c r="P73">
-        <v>-524.1591330133333</v>
+        <v>-536.2079470933334</v>
       </c>
       <c r="Q73">
-        <v>-192.5591330133333</v>
+        <v>-204.6079470933334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1200607412990499</v>
+        <v>0.1227129106311588</v>
       </c>
       <c r="T73">
-        <v>1.447480069363576</v>
+        <v>1.49917578612656</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07745643760173626</v>
+        <v>0.0763806537461566</v>
       </c>
       <c r="W73">
-        <v>0.2175357720135106</v>
+        <v>0.2177894418466563</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3872821880086813</v>
+        <v>0.381903268730783</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.191168013106317</v>
+        <v>0.193068013106317</v>
       </c>
       <c r="C74">
-        <v>-3353.319903851294</v>
+        <v>-3429.149977743492</v>
       </c>
       <c r="D74">
-        <v>926.8640961487057</v>
+        <v>914.9060222565076</v>
       </c>
       <c r="E74">
-        <v>1860.684</v>
+        <v>1924.556</v>
       </c>
       <c r="F74">
-        <v>4598.784</v>
+        <v>4662.656</v>
       </c>
       <c r="G74">
         <v>318.6</v>
@@ -7349,37 +7349,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M74">
-        <v>1084.3932672</v>
+        <v>1099.4542848</v>
       </c>
       <c r="N74">
-        <v>-670.2599338666666</v>
+        <v>-685.3209514666669</v>
       </c>
       <c r="O74">
-        <v>-134.0519867733333</v>
+        <v>-137.0641902933334</v>
       </c>
       <c r="P74">
-        <v>-536.2079470933334</v>
+        <v>-548.2567611733335</v>
       </c>
       <c r="Q74">
-        <v>-204.6079470933334</v>
+        <v>-216.6567611733336</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1227129106311588</v>
+        <v>0.1255615369508314</v>
       </c>
       <c r="T74">
-        <v>1.49917578612656</v>
+        <v>1.554700815242359</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0763806537461566</v>
+        <v>0.07533434342086676</v>
       </c>
       <c r="W74">
-        <v>0.2177894418466563</v>
+        <v>0.2180361618213596</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.381903268730783</v>
+        <v>0.3766717171043338</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.193068013106317</v>
+        <v>0.194968013106317</v>
       </c>
       <c r="C75">
-        <v>-3429.149977743492</v>
+        <v>-3504.675424123102</v>
       </c>
       <c r="D75">
-        <v>914.9060222565076</v>
+        <v>903.2525758768977</v>
       </c>
       <c r="E75">
-        <v>1924.556</v>
+        <v>1988.428</v>
       </c>
       <c r="F75">
-        <v>4662.656</v>
+        <v>4726.528</v>
       </c>
       <c r="G75">
         <v>318.6</v>
@@ -7431,37 +7431,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M75">
-        <v>1099.4542848</v>
+        <v>1114.5153024</v>
       </c>
       <c r="N75">
-        <v>-685.3209514666669</v>
+        <v>-700.3819690666669</v>
       </c>
       <c r="O75">
-        <v>-137.0641902933334</v>
+        <v>-140.0763938133334</v>
       </c>
       <c r="P75">
-        <v>-548.2567611733335</v>
+        <v>-560.3055752533335</v>
       </c>
       <c r="Q75">
-        <v>-216.6567611733336</v>
+        <v>-228.7055752533335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1255615369508314</v>
+        <v>0.1286292883720172</v>
       </c>
       <c r="T75">
-        <v>1.554700815242359</v>
+        <v>1.614497000443988</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07533434342086676</v>
+        <v>0.07431631175301721</v>
       </c>
       <c r="W75">
-        <v>0.2180361618213596</v>
+        <v>0.2182762136886386</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3766717171043338</v>
+        <v>0.371581558765086</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.194968013106317</v>
+        <v>0.196868013106317</v>
       </c>
       <c r="C76">
-        <v>-3504.675424123102</v>
+        <v>-3579.907736997266</v>
       </c>
       <c r="D76">
-        <v>903.2525758768977</v>
+        <v>891.8922630027334</v>
       </c>
       <c r="E76">
-        <v>1988.428</v>
+        <v>2052.3</v>
       </c>
       <c r="F76">
-        <v>4726.528</v>
+        <v>4790.4</v>
       </c>
       <c r="G76">
         <v>318.6</v>
@@ -7513,37 +7513,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M76">
-        <v>1114.5153024</v>
+        <v>1129.57632</v>
       </c>
       <c r="N76">
-        <v>-700.3819690666669</v>
+        <v>-715.4429866666667</v>
       </c>
       <c r="O76">
-        <v>-140.0763938133334</v>
+        <v>-143.0885973333334</v>
       </c>
       <c r="P76">
-        <v>-560.3055752533335</v>
+        <v>-572.3543893333333</v>
       </c>
       <c r="Q76">
-        <v>-228.7055752533335</v>
+        <v>-240.7543893333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1286292883720172</v>
+        <v>0.1319424599068979</v>
       </c>
       <c r="T76">
-        <v>1.614497000443988</v>
+        <v>1.679076880461748</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07431631175301721</v>
+        <v>0.07332542759631032</v>
       </c>
       <c r="W76">
-        <v>0.2182762136886386</v>
+        <v>0.21850986417279</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.371581558765086</v>
+        <v>0.3666271379815516</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.196868013106317</v>
+        <v>0.198768013106317</v>
       </c>
       <c r="C77">
-        <v>-3579.907736997266</v>
+        <v>-3654.857839309593</v>
       </c>
       <c r="D77">
-        <v>891.8922630027334</v>
+        <v>880.8141606904067</v>
       </c>
       <c r="E77">
-        <v>2052.3</v>
+        <v>2116.172</v>
       </c>
       <c r="F77">
-        <v>4790.4</v>
+        <v>4854.272</v>
       </c>
       <c r="G77">
         <v>318.6</v>
@@ -7595,37 +7595,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M77">
-        <v>1129.57632</v>
+        <v>1144.6373376</v>
       </c>
       <c r="N77">
-        <v>-715.4429866666667</v>
+        <v>-730.5040042666669</v>
       </c>
       <c r="O77">
-        <v>-143.0885973333334</v>
+        <v>-146.1008008533334</v>
       </c>
       <c r="P77">
-        <v>-572.3543893333333</v>
+        <v>-584.4032034133336</v>
       </c>
       <c r="Q77">
-        <v>-240.7543893333333</v>
+        <v>-252.8032034133336</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1319424599068979</v>
+        <v>0.1355317290696853</v>
       </c>
       <c r="T77">
-        <v>1.679076880461748</v>
+        <v>1.749038417147654</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07332542759631032</v>
+        <v>0.07236061933846412</v>
       </c>
       <c r="W77">
-        <v>0.21850986417279</v>
+        <v>0.2187373659599902</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3666271379815516</v>
+        <v>0.3618030966923206</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.198768013106317</v>
+        <v>0.200668013106317</v>
       </c>
       <c r="C78">
-        <v>-3654.857839309593</v>
+        <v>-3729.536117970656</v>
       </c>
       <c r="D78">
-        <v>880.8141606904067</v>
+        <v>870.0078820293446</v>
       </c>
       <c r="E78">
-        <v>2116.172</v>
+        <v>2180.044</v>
       </c>
       <c r="F78">
-        <v>4854.272</v>
+        <v>4918.144</v>
       </c>
       <c r="G78">
         <v>318.6</v>
@@ -7677,37 +7677,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M78">
-        <v>1144.6373376</v>
+        <v>1159.6983552</v>
       </c>
       <c r="N78">
-        <v>-730.5040042666669</v>
+        <v>-745.5650218666669</v>
       </c>
       <c r="O78">
-        <v>-146.1008008533334</v>
+        <v>-149.1130043733334</v>
       </c>
       <c r="P78">
-        <v>-584.4032034133336</v>
+        <v>-596.4520174933335</v>
       </c>
       <c r="Q78">
-        <v>-252.8032034133336</v>
+        <v>-264.8520174933336</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1355317290696853</v>
+        <v>0.1394331085944542</v>
       </c>
       <c r="T78">
-        <v>1.749038417147654</v>
+        <v>1.825083565719291</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07236061933846412</v>
+        <v>0.07142087103536719</v>
       </c>
       <c r="W78">
-        <v>0.2187373659599902</v>
+        <v>0.2189589586098604</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3618030966923206</v>
+        <v>0.3571043551768359</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.200668013106317</v>
+        <v>0.202568013106317</v>
       </c>
       <c r="C79">
-        <v>-3729.536117970656</v>
+        <v>-3803.952456341102</v>
       </c>
       <c r="D79">
-        <v>870.0078820293446</v>
+        <v>859.4635436588976</v>
       </c>
       <c r="E79">
-        <v>2180.044</v>
+        <v>2243.916</v>
       </c>
       <c r="F79">
-        <v>4918.144</v>
+        <v>4982.016</v>
       </c>
       <c r="G79">
         <v>318.6</v>
@@ -7759,37 +7759,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M79">
-        <v>1159.6983552</v>
+        <v>1174.7593728</v>
       </c>
       <c r="N79">
-        <v>-745.5650218666669</v>
+        <v>-760.6260394666667</v>
       </c>
       <c r="O79">
-        <v>-149.1130043733334</v>
+        <v>-152.1252078933333</v>
       </c>
       <c r="P79">
-        <v>-596.4520174933335</v>
+        <v>-608.5008315733334</v>
       </c>
       <c r="Q79">
-        <v>-264.8520174933336</v>
+        <v>-276.9008315733334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1394331085944542</v>
+        <v>0.1436891589851112</v>
       </c>
       <c r="T79">
-        <v>1.825083565719291</v>
+        <v>1.908041909615622</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07142087103536719</v>
+        <v>0.07050521884260608</v>
       </c>
       <c r="W79">
-        <v>0.2189589586098604</v>
+        <v>0.2191748693969135</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3571043551768359</v>
+        <v>0.3525260942130304</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.202568013106317</v>
+        <v>0.204468013106317</v>
       </c>
       <c r="C80">
-        <v>-3803.952456341102</v>
+        <v>-3878.116264380936</v>
       </c>
       <c r="D80">
-        <v>859.4635436588976</v>
+        <v>849.1717356190644</v>
       </c>
       <c r="E80">
-        <v>2243.916</v>
+        <v>2307.788</v>
       </c>
       <c r="F80">
-        <v>4982.016</v>
+        <v>5045.888</v>
       </c>
       <c r="G80">
         <v>318.6</v>
@@ -7841,37 +7841,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M80">
-        <v>1174.7593728</v>
+        <v>1189.8203904</v>
       </c>
       <c r="N80">
-        <v>-760.6260394666667</v>
+        <v>-775.6870570666667</v>
       </c>
       <c r="O80">
-        <v>-152.1252078933333</v>
+        <v>-155.1374114133334</v>
       </c>
       <c r="P80">
-        <v>-608.5008315733334</v>
+        <v>-620.5496456533334</v>
       </c>
       <c r="Q80">
-        <v>-276.9008315733334</v>
+        <v>-288.9496456533334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1436891589851112</v>
+        <v>0.1483505475082118</v>
       </c>
       <c r="T80">
-        <v>1.908041909615622</v>
+        <v>1.998901048168748</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07050521884260608</v>
+        <v>0.06961274771801612</v>
       </c>
       <c r="W80">
-        <v>0.2191748693969135</v>
+        <v>0.2193853140880918</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3525260942130304</v>
+        <v>0.3480637385900806</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.204468013106317</v>
+        <v>0.206368013106317</v>
       </c>
       <c r="C81">
-        <v>-3878.116264380936</v>
+        <v>-3952.036506658231</v>
       </c>
       <c r="D81">
-        <v>849.1717356190644</v>
+        <v>839.1234933417691</v>
       </c>
       <c r="E81">
-        <v>2307.788</v>
+        <v>2371.66</v>
       </c>
       <c r="F81">
-        <v>5045.888</v>
+        <v>5109.76</v>
       </c>
       <c r="G81">
         <v>318.6</v>
@@ -7923,37 +7923,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M81">
-        <v>1189.8203904</v>
+        <v>1204.881408</v>
       </c>
       <c r="N81">
-        <v>-775.6870570666667</v>
+        <v>-790.748074666667</v>
       </c>
       <c r="O81">
-        <v>-155.1374114133334</v>
+        <v>-158.1496149333334</v>
       </c>
       <c r="P81">
-        <v>-620.5496456533334</v>
+        <v>-632.5984597333336</v>
       </c>
       <c r="Q81">
-        <v>-288.9496456533334</v>
+        <v>-300.9984597333336</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1483505475082118</v>
+        <v>0.1534780748836224</v>
       </c>
       <c r="T81">
-        <v>1.998901048168748</v>
+        <v>2.098846100577185</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06961274771801612</v>
+        <v>0.06874258837154092</v>
       </c>
       <c r="W81">
-        <v>0.2193853140880918</v>
+        <v>0.2195904976619907</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3480637385900806</v>
+        <v>0.3437129418577045</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.206368013106317</v>
+        <v>0.208268013106317</v>
       </c>
       <c r="C82">
-        <v>-3952.036506658231</v>
+        <v>-4025.721728392568</v>
       </c>
       <c r="D82">
-        <v>839.1234933417691</v>
+        <v>829.3102716074325</v>
       </c>
       <c r="E82">
-        <v>2371.66</v>
+        <v>2435.532000000001</v>
       </c>
       <c r="F82">
-        <v>5109.76</v>
+        <v>5173.632000000001</v>
       </c>
       <c r="G82">
         <v>318.6</v>
@@ -8005,37 +8005,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M82">
-        <v>1204.881408</v>
+        <v>1219.9424256</v>
       </c>
       <c r="N82">
-        <v>-790.748074666667</v>
+        <v>-805.809092266667</v>
       </c>
       <c r="O82">
-        <v>-158.1496149333334</v>
+        <v>-161.1618184533334</v>
       </c>
       <c r="P82">
-        <v>-632.5984597333336</v>
+        <v>-644.6472738133336</v>
       </c>
       <c r="Q82">
-        <v>-300.9984597333336</v>
+        <v>-313.0472738133337</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1534780748836224</v>
+        <v>0.1591453419827604</v>
       </c>
       <c r="T82">
-        <v>2.098846100577185</v>
+        <v>2.20931168481809</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06874258837154092</v>
+        <v>0.06789391444102806</v>
       </c>
       <c r="W82">
-        <v>0.2195904976619907</v>
+        <v>0.2197906149748056</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3437129418577045</v>
+        <v>0.3394695722051403</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.208268013106317</v>
+        <v>0.210168013106317</v>
       </c>
       <c r="C83">
-        <v>-4025.721728392568</v>
+        <v>-4099.180079692165</v>
       </c>
       <c r="D83">
-        <v>829.3102716074325</v>
+        <v>819.7239203078343</v>
       </c>
       <c r="E83">
-        <v>2435.532000000001</v>
+        <v>2499.404</v>
       </c>
       <c r="F83">
-        <v>5173.632000000001</v>
+        <v>5237.504</v>
       </c>
       <c r="G83">
         <v>318.6</v>
@@ -8087,37 +8087,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M83">
-        <v>1219.9424256</v>
+        <v>1235.0034432</v>
       </c>
       <c r="N83">
-        <v>-805.809092266667</v>
+        <v>-820.8701098666668</v>
       </c>
       <c r="O83">
-        <v>-161.1618184533334</v>
+        <v>-164.1740219733334</v>
       </c>
       <c r="P83">
-        <v>-644.6472738133336</v>
+        <v>-656.6960878933335</v>
       </c>
       <c r="Q83">
-        <v>-313.0472738133337</v>
+        <v>-325.0960878933335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1591453419827604</v>
+        <v>0.1654423054262471</v>
       </c>
       <c r="T83">
-        <v>2.20931168481809</v>
+        <v>2.332051222863539</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06789391444102806</v>
+        <v>0.06706593987467407</v>
       </c>
       <c r="W83">
-        <v>0.2197906149748056</v>
+        <v>0.2199858513775519</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3394695722051403</v>
+        <v>0.3353296993733703</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.210168013106317</v>
+        <v>0.212068013106317</v>
       </c>
       <c r="C84">
-        <v>-4099.180079692165</v>
+        <v>-4172.419338129235</v>
       </c>
       <c r="D84">
-        <v>819.7239203078343</v>
+        <v>810.3566618707653</v>
       </c>
       <c r="E84">
-        <v>2499.404</v>
+        <v>2563.276</v>
       </c>
       <c r="F84">
-        <v>5237.504</v>
+        <v>5301.376</v>
       </c>
       <c r="G84">
         <v>318.6</v>
@@ -8169,37 +8169,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M84">
-        <v>1235.0034432</v>
+        <v>1250.0644608</v>
       </c>
       <c r="N84">
-        <v>-820.8701098666668</v>
+        <v>-835.9311274666668</v>
       </c>
       <c r="O84">
-        <v>-164.1740219733334</v>
+        <v>-167.1862254933334</v>
       </c>
       <c r="P84">
-        <v>-656.6960878933335</v>
+        <v>-668.7449019733334</v>
       </c>
       <c r="Q84">
-        <v>-325.0960878933335</v>
+        <v>-337.1449019733334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1654423054262471</v>
+        <v>0.1724800880983793</v>
       </c>
       <c r="T84">
-        <v>2.332051222863539</v>
+        <v>2.469230706561395</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06706593987467407</v>
+        <v>0.06625791650269006</v>
       </c>
       <c r="W84">
-        <v>0.2199858513775519</v>
+        <v>0.2201763832886657</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3353296993733703</v>
+        <v>0.3312895825134502</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.212068013106317</v>
+        <v>0.213968013106317</v>
       </c>
       <c r="C85">
-        <v>-4172.419338129235</v>
+        <v>-4245.44692978495</v>
       </c>
       <c r="D85">
-        <v>810.3566618707653</v>
+        <v>801.2010702150499</v>
       </c>
       <c r="E85">
-        <v>2563.276</v>
+        <v>2627.148000000001</v>
       </c>
       <c r="F85">
-        <v>5301.376</v>
+        <v>5365.248000000001</v>
       </c>
       <c r="G85">
         <v>318.6</v>
@@ -8251,37 +8251,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M85">
-        <v>1250.0644608</v>
+        <v>1265.1254784</v>
       </c>
       <c r="N85">
-        <v>-835.9311274666668</v>
+        <v>-850.992145066667</v>
       </c>
       <c r="O85">
-        <v>-167.1862254933334</v>
+        <v>-170.1984290133334</v>
       </c>
       <c r="P85">
-        <v>-668.7449019733334</v>
+        <v>-680.7937160533336</v>
       </c>
       <c r="Q85">
-        <v>-337.1449019733334</v>
+        <v>-349.1937160533336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1724800880983793</v>
+        <v>0.180397593604528</v>
       </c>
       <c r="T85">
-        <v>2.469230706561395</v>
+        <v>2.623557625721483</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06625791650269006</v>
+        <v>0.06546913178241991</v>
       </c>
       <c r="W85">
-        <v>0.2201763832886657</v>
+        <v>0.2203623787257054</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3312895825134502</v>
+        <v>0.3273456589120995</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.213968013106317</v>
+        <v>0.215868013106317</v>
       </c>
       <c r="C86">
-        <v>-4245.44692978495</v>
+        <v>-4318.269948883744</v>
       </c>
       <c r="D86">
-        <v>801.2010702150499</v>
+        <v>792.2500511162556</v>
       </c>
       <c r="E86">
-        <v>2627.148</v>
+        <v>2691.02</v>
       </c>
       <c r="F86">
-        <v>5365.248</v>
+        <v>5429.12</v>
       </c>
       <c r="G86">
         <v>318.6</v>
@@ -8333,37 +8333,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M86">
-        <v>1265.1254784</v>
+        <v>1280.186496</v>
       </c>
       <c r="N86">
-        <v>-850.9921450666668</v>
+        <v>-866.0531626666668</v>
       </c>
       <c r="O86">
-        <v>-170.1984290133334</v>
+        <v>-173.2106325333334</v>
       </c>
       <c r="P86">
-        <v>-680.7937160533335</v>
+        <v>-692.8425301333334</v>
       </c>
       <c r="Q86">
-        <v>-349.1937160533335</v>
+        <v>-361.2425301333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.180397593604528</v>
+        <v>0.1893707665114965</v>
       </c>
       <c r="T86">
-        <v>2.623557625721481</v>
+        <v>2.798461467436246</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06546913178241992</v>
+        <v>0.06469890670262675</v>
       </c>
       <c r="W86">
-        <v>0.2203623787257054</v>
+        <v>0.2205439977995206</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3273456589120995</v>
+        <v>0.3234945335131337</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.215868013106317</v>
+        <v>0.217768013106317</v>
       </c>
       <c r="C87">
-        <v>-4318.269948883744</v>
+        <v>-4390.895176126012</v>
       </c>
       <c r="D87">
-        <v>792.2500511162556</v>
+        <v>783.4968238739876</v>
       </c>
       <c r="E87">
-        <v>2691.02</v>
+        <v>2754.892</v>
       </c>
       <c r="F87">
-        <v>5429.12</v>
+        <v>5492.992</v>
       </c>
       <c r="G87">
         <v>318.6</v>
@@ -8415,37 +8415,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M87">
-        <v>1280.186496</v>
+        <v>1295.2475136</v>
       </c>
       <c r="N87">
-        <v>-866.0531626666668</v>
+        <v>-881.1141802666668</v>
       </c>
       <c r="O87">
-        <v>-173.2106325333334</v>
+        <v>-176.2228360533334</v>
       </c>
       <c r="P87">
-        <v>-692.8425301333334</v>
+        <v>-704.8913442133335</v>
       </c>
       <c r="Q87">
-        <v>-361.2425301333334</v>
+        <v>-373.2913442133335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1893707665114965</v>
+        <v>0.1996258212623176</v>
       </c>
       <c r="T87">
-        <v>2.798461467436246</v>
+        <v>2.998351572253121</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06469890670262675</v>
+        <v>0.06394659383399155</v>
       </c>
       <c r="W87">
-        <v>0.2205439977995206</v>
+        <v>0.2207213931739448</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3234945335131337</v>
+        <v>0.3197329691699577</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.217768013106317</v>
+        <v>0.219668013106317</v>
       </c>
       <c r="C88">
-        <v>-4390.895176126012</v>
+        <v>-4463.329095818798</v>
       </c>
       <c r="D88">
-        <v>783.4968238739876</v>
+        <v>774.9349041812017</v>
       </c>
       <c r="E88">
-        <v>2754.892</v>
+        <v>2818.764</v>
       </c>
       <c r="F88">
-        <v>5492.992</v>
+        <v>5556.864</v>
       </c>
       <c r="G88">
         <v>318.6</v>
@@ -8497,37 +8497,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M88">
-        <v>1295.2475136</v>
+        <v>1310.3085312</v>
       </c>
       <c r="N88">
-        <v>-881.1141802666668</v>
+        <v>-896.1751978666668</v>
       </c>
       <c r="O88">
-        <v>-176.2228360533334</v>
+        <v>-179.2350395733334</v>
       </c>
       <c r="P88">
-        <v>-704.8913442133335</v>
+        <v>-716.9401582933335</v>
       </c>
       <c r="Q88">
-        <v>-373.2913442133335</v>
+        <v>-385.3401582933336</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1996258212623176</v>
+        <v>0.2114585767440344</v>
       </c>
       <c r="T88">
-        <v>2.998351572253121</v>
+        <v>3.228994000887977</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06394659383399155</v>
+        <v>0.06321157551406062</v>
       </c>
       <c r="W88">
-        <v>0.2207213931739448</v>
+        <v>0.2208947104937845</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3197329691699577</v>
+        <v>0.316057877570303</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.219668013106317</v>
+        <v>0.221568013106317</v>
       </c>
       <c r="C89">
-        <v>-4463.329095818798</v>
+        <v>-4535.577911895416</v>
       </c>
       <c r="D89">
-        <v>774.9349041812017</v>
+        <v>766.5580881045832</v>
       </c>
       <c r="E89">
-        <v>2818.764</v>
+        <v>2882.636</v>
       </c>
       <c r="F89">
-        <v>5556.864</v>
+        <v>5620.736</v>
       </c>
       <c r="G89">
         <v>318.6</v>
@@ -8579,37 +8579,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M89">
-        <v>1310.3085312</v>
+        <v>1325.3695488</v>
       </c>
       <c r="N89">
-        <v>-896.1751978666668</v>
+        <v>-911.2362154666669</v>
       </c>
       <c r="O89">
-        <v>-179.2350395733334</v>
+        <v>-182.2472430933334</v>
       </c>
       <c r="P89">
-        <v>-716.9401582933335</v>
+        <v>-728.9889723733335</v>
       </c>
       <c r="Q89">
-        <v>-385.3401582933336</v>
+        <v>-397.3889723733335</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2114585767440344</v>
+        <v>0.2252634581393706</v>
       </c>
       <c r="T89">
-        <v>3.228994000887977</v>
+        <v>3.498076834295308</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06321157551406062</v>
+        <v>0.0624932621559463</v>
       </c>
       <c r="W89">
-        <v>0.2208947104937845</v>
+        <v>0.2210640887836279</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.316057877570303</v>
+        <v>0.3124663107797314</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.221568013106317</v>
+        <v>0.223468013106317</v>
       </c>
       <c r="C90">
-        <v>-4535.577911895416</v>
+        <v>-4607.647562907179</v>
       </c>
       <c r="D90">
-        <v>766.5580881045832</v>
+        <v>758.3604370928215</v>
       </c>
       <c r="E90">
-        <v>2882.636</v>
+        <v>2946.508</v>
       </c>
       <c r="F90">
-        <v>5620.736</v>
+        <v>5684.608</v>
       </c>
       <c r="G90">
         <v>318.6</v>
@@ -8661,37 +8661,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M90">
-        <v>1325.3695488</v>
+        <v>1340.4305664</v>
       </c>
       <c r="N90">
-        <v>-911.2362154666669</v>
+        <v>-926.2972330666669</v>
       </c>
       <c r="O90">
-        <v>-182.2472430933334</v>
+        <v>-185.2594466133334</v>
       </c>
       <c r="P90">
-        <v>-728.9889723733335</v>
+        <v>-741.0377864533335</v>
       </c>
       <c r="Q90">
-        <v>-397.3889723733335</v>
+        <v>-409.4377864533336</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2252634581393706</v>
+        <v>0.2415783179702225</v>
       </c>
       <c r="T90">
-        <v>3.498076834295308</v>
+        <v>3.816083819231245</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0624932621559463</v>
+        <v>0.06179109067104802</v>
       </c>
       <c r="W90">
-        <v>0.2210640887836279</v>
+        <v>0.2212296608197669</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3124663107797314</v>
+        <v>0.30895545335524</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.223468013106317</v>
+        <v>0.225368013106317</v>
       </c>
       <c r="C91">
-        <v>-4607.647562907179</v>
+        <v>-4679.543736063359</v>
       </c>
       <c r="D91">
-        <v>758.3604370928215</v>
+        <v>750.3362639366408</v>
       </c>
       <c r="E91">
-        <v>2946.508</v>
+        <v>3010.38</v>
       </c>
       <c r="F91">
-        <v>5684.608</v>
+        <v>5748.48</v>
       </c>
       <c r="G91">
         <v>318.6</v>
@@ -8743,37 +8743,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M91">
-        <v>1340.4305664</v>
+        <v>1355.491584</v>
       </c>
       <c r="N91">
-        <v>-926.2972330666669</v>
+        <v>-941.3582506666667</v>
       </c>
       <c r="O91">
-        <v>-185.2594466133334</v>
+        <v>-188.2716501333333</v>
       </c>
       <c r="P91">
-        <v>-741.0377864533335</v>
+        <v>-753.0866005333334</v>
       </c>
       <c r="Q91">
-        <v>-409.4377864533336</v>
+        <v>-421.4866005333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2415783179702225</v>
+        <v>0.2611561497672448</v>
       </c>
       <c r="T91">
-        <v>3.816083819231245</v>
+        <v>4.19769220115437</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06179109067104802</v>
+        <v>0.06110452299692527</v>
       </c>
       <c r="W91">
-        <v>0.2212296608197669</v>
+        <v>0.221391553477325</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.30895545335524</v>
+        <v>0.3055226149846263</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.225368013106317</v>
+        <v>0.227268013106317</v>
       </c>
       <c r="C92">
-        <v>-4679.543736063359</v>
+        <v>-4751.27188038916</v>
       </c>
       <c r="D92">
-        <v>750.3362639366408</v>
+        <v>742.4801196108393</v>
       </c>
       <c r="E92">
-        <v>3010.38</v>
+        <v>3074.252</v>
       </c>
       <c r="F92">
-        <v>5748.48</v>
+        <v>5812.352</v>
       </c>
       <c r="G92">
         <v>318.6</v>
@@ -8825,37 +8825,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M92">
-        <v>1355.491584</v>
+        <v>1370.5526016</v>
       </c>
       <c r="N92">
-        <v>-941.3582506666667</v>
+        <v>-956.4192682666669</v>
       </c>
       <c r="O92">
-        <v>-188.2716501333333</v>
+        <v>-191.2838536533334</v>
       </c>
       <c r="P92">
-        <v>-753.0866005333334</v>
+        <v>-765.1354146133335</v>
       </c>
       <c r="Q92">
-        <v>-421.4866005333334</v>
+        <v>-433.5354146133336</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2611561497672448</v>
+        <v>0.2850846108524942</v>
       </c>
       <c r="T92">
-        <v>4.19769220115437</v>
+        <v>4.664102445727079</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06110452299692527</v>
+        <v>0.06043304472223378</v>
       </c>
       <c r="W92">
-        <v>0.221391553477325</v>
+        <v>0.2215498880544973</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3055226149846263</v>
+        <v>0.3021652236111688</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.227268013106317</v>
+        <v>0.229168013106317</v>
       </c>
       <c r="C93">
-        <v>-4751.27188038916</v>
+        <v>-4822.837219065643</v>
       </c>
       <c r="D93">
-        <v>742.4801196108393</v>
+        <v>734.786780934357</v>
       </c>
       <c r="E93">
-        <v>3074.252</v>
+        <v>3138.124</v>
       </c>
       <c r="F93">
-        <v>5812.352</v>
+        <v>5876.224</v>
       </c>
       <c r="G93">
         <v>318.6</v>
@@ -8907,37 +8907,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M93">
-        <v>1370.5526016</v>
+        <v>1385.6136192</v>
       </c>
       <c r="N93">
-        <v>-956.4192682666669</v>
+        <v>-971.4802858666669</v>
       </c>
       <c r="O93">
-        <v>-191.2838536533334</v>
+        <v>-194.2960571733334</v>
       </c>
       <c r="P93">
-        <v>-765.1354146133335</v>
+        <v>-777.1842286933336</v>
       </c>
       <c r="Q93">
-        <v>-433.5354146133336</v>
+        <v>-445.5842286933336</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2850846108524942</v>
+        <v>0.3149951872090561</v>
       </c>
       <c r="T93">
-        <v>4.664102445727079</v>
+        <v>5.247115251442965</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06043304472223378</v>
+        <v>0.05977616380133993</v>
       </c>
       <c r="W93">
-        <v>0.2215498880544973</v>
+        <v>0.2217047805756441</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3021652236111688</v>
+        <v>0.2988808190066996</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.229168013106317</v>
+        <v>0.231068013106317</v>
       </c>
       <c r="C94">
-        <v>-4822.837219065643</v>
+        <v>-4894.244761010351</v>
       </c>
       <c r="D94">
-        <v>734.786780934357</v>
+        <v>727.2512389896496</v>
       </c>
       <c r="E94">
-        <v>3138.124</v>
+        <v>3201.996000000001</v>
       </c>
       <c r="F94">
-        <v>5876.224</v>
+        <v>5940.096</v>
       </c>
       <c r="G94">
         <v>318.6</v>
@@ -8989,37 +8989,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M94">
-        <v>1385.6136192</v>
+        <v>1400.6746368</v>
       </c>
       <c r="N94">
-        <v>-971.4802858666669</v>
+        <v>-986.5413034666669</v>
       </c>
       <c r="O94">
-        <v>-194.2960571733334</v>
+        <v>-197.3082606933334</v>
       </c>
       <c r="P94">
-        <v>-777.1842286933336</v>
+        <v>-789.2330427733335</v>
       </c>
       <c r="Q94">
-        <v>-445.5842286933336</v>
+        <v>-457.6330427733336</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3149951872090561</v>
+        <v>0.3534516425246355</v>
       </c>
       <c r="T94">
-        <v>5.247115251442965</v>
+        <v>5.996703144506246</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05977616380133993</v>
+        <v>0.05913340935186315</v>
       </c>
       <c r="W94">
-        <v>0.2217047805756441</v>
+        <v>0.2218563420748307</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2988808190066996</v>
+        <v>0.2956670467593158</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.231068013106317</v>
+        <v>0.232968013106317</v>
       </c>
       <c r="C95">
-        <v>-4894.244761010351</v>
+        <v>-4965.499311752584</v>
       </c>
       <c r="D95">
-        <v>727.2512389896496</v>
+        <v>719.8686882474162</v>
       </c>
       <c r="E95">
-        <v>3201.996000000001</v>
+        <v>3265.868</v>
       </c>
       <c r="F95">
-        <v>5940.096</v>
+        <v>6003.968</v>
       </c>
       <c r="G95">
         <v>318.6</v>
@@ -9071,37 +9071,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M95">
-        <v>1400.6746368</v>
+        <v>1415.7356544</v>
       </c>
       <c r="N95">
-        <v>-986.5413034666669</v>
+        <v>-1001.602321066667</v>
       </c>
       <c r="O95">
-        <v>-197.3082606933334</v>
+        <v>-200.3204642133334</v>
       </c>
       <c r="P95">
-        <v>-789.2330427733335</v>
+        <v>-801.2818568533334</v>
       </c>
       <c r="Q95">
-        <v>-457.6330427733336</v>
+        <v>-469.6818568533334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3534516425246355</v>
+        <v>0.4047269162787415</v>
       </c>
       <c r="T95">
-        <v>5.996703144506246</v>
+        <v>6.996153668590622</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05913340935186315</v>
+        <v>0.05850433052897101</v>
       </c>
       <c r="W95">
-        <v>0.2218563420748307</v>
+        <v>0.2220046788612687</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2956670467593158</v>
+        <v>0.292521652644855</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.232968013106317</v>
+        <v>0.234868013106317</v>
       </c>
       <c r="C96">
-        <v>-4965.499311752584</v>
+        <v>-5036.60548365294</v>
       </c>
       <c r="D96">
-        <v>719.8686882474162</v>
+        <v>712.6345163470594</v>
       </c>
       <c r="E96">
-        <v>3265.868</v>
+        <v>3329.74</v>
       </c>
       <c r="F96">
-        <v>6003.968</v>
+        <v>6067.84</v>
       </c>
       <c r="G96">
         <v>318.6</v>
@@ -9153,37 +9153,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M96">
-        <v>1415.7356544</v>
+        <v>1430.796672</v>
       </c>
       <c r="N96">
-        <v>-1001.602321066667</v>
+        <v>-1016.663338666667</v>
       </c>
       <c r="O96">
-        <v>-200.3204642133334</v>
+        <v>-203.3326677333334</v>
       </c>
       <c r="P96">
-        <v>-801.2818568533334</v>
+        <v>-813.3306709333335</v>
       </c>
       <c r="Q96">
-        <v>-469.6818568533334</v>
+        <v>-481.7306709333336</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4047269162787415</v>
+        <v>0.47651229953449</v>
       </c>
       <c r="T96">
-        <v>6.996153668590622</v>
+        <v>8.395384402308752</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05850433052897101</v>
+        <v>0.0578884954707713</v>
       </c>
       <c r="W96">
-        <v>0.2220046788612687</v>
+        <v>0.2221498927679922</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.292521652644855</v>
+        <v>0.2894424773538564</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.234868013106317</v>
+        <v>0.236768013106317</v>
       </c>
       <c r="C97">
-        <v>-5036.60548365294</v>
+        <v>-5107.567705512796</v>
       </c>
       <c r="D97">
-        <v>712.6345163470594</v>
+        <v>705.5442944872044</v>
       </c>
       <c r="E97">
-        <v>3329.74</v>
+        <v>3393.612000000001</v>
       </c>
       <c r="F97">
-        <v>6067.84</v>
+        <v>6131.712</v>
       </c>
       <c r="G97">
         <v>318.6</v>
@@ -9235,37 +9235,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M97">
-        <v>1430.796672</v>
+        <v>1445.8576896</v>
       </c>
       <c r="N97">
-        <v>-1016.663338666667</v>
+        <v>-1031.724356266667</v>
       </c>
       <c r="O97">
-        <v>-203.3326677333334</v>
+        <v>-206.3448712533334</v>
       </c>
       <c r="P97">
-        <v>-813.3306709333335</v>
+        <v>-825.3794850133336</v>
       </c>
       <c r="Q97">
-        <v>-481.7306709333336</v>
+        <v>-493.7794850133336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.47651229953449</v>
+        <v>0.5841903744181127</v>
       </c>
       <c r="T97">
-        <v>8.395384402308752</v>
+        <v>10.49423050288594</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0578884954707713</v>
+        <v>0.05728549030961743</v>
       </c>
       <c r="W97">
-        <v>0.2221498927679922</v>
+        <v>0.2222920813849922</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2894424773538564</v>
+        <v>0.2864274515480871</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.236768013106317</v>
+        <v>0.238668013106317</v>
       </c>
       <c r="C98">
-        <v>-5107.567705512795</v>
+        <v>-5178.390231615777</v>
       </c>
       <c r="D98">
-        <v>705.5442944872044</v>
+        <v>698.5937683842228</v>
       </c>
       <c r="E98">
-        <v>3393.612</v>
+        <v>3457.484</v>
       </c>
       <c r="F98">
-        <v>6131.712</v>
+        <v>6195.584</v>
       </c>
       <c r="G98">
         <v>318.6</v>
@@ -9317,37 +9317,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M98">
-        <v>1445.8576896</v>
+        <v>1460.9187072</v>
       </c>
       <c r="N98">
-        <v>-1031.724356266667</v>
+        <v>-1046.785373866667</v>
       </c>
       <c r="O98">
-        <v>-206.3448712533334</v>
+        <v>-209.3570747733334</v>
       </c>
       <c r="P98">
-        <v>-825.3794850133334</v>
+        <v>-837.4282990933334</v>
       </c>
       <c r="Q98">
-        <v>-493.7794850133334</v>
+        <v>-505.8282990933334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5841903744181113</v>
+        <v>0.7636538325574818</v>
       </c>
       <c r="T98">
-        <v>10.49423050288592</v>
+        <v>13.99230733718122</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05728549030961744</v>
+        <v>0.05669491824456984</v>
       </c>
       <c r="W98">
-        <v>0.2222920813849922</v>
+        <v>0.2224313382779304</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2864274515480871</v>
+        <v>0.2834745912228491</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.238668013106317</v>
+        <v>0.240568013106317</v>
       </c>
       <c r="C99">
-        <v>-5178.390231615777</v>
+        <v>-5249.077150240046</v>
       </c>
       <c r="D99">
-        <v>698.5937683842228</v>
+        <v>691.7788497599544</v>
       </c>
       <c r="E99">
-        <v>3457.484</v>
+        <v>3521.356</v>
       </c>
       <c r="F99">
-        <v>6195.584</v>
+        <v>6259.456</v>
       </c>
       <c r="G99">
         <v>318.6</v>
@@ -9399,37 +9399,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M99">
-        <v>1460.9187072</v>
+        <v>1475.9797248</v>
       </c>
       <c r="N99">
-        <v>-1046.785373866667</v>
+        <v>-1061.846391466667</v>
       </c>
       <c r="O99">
-        <v>-209.3570747733334</v>
+        <v>-212.3692782933334</v>
       </c>
       <c r="P99">
-        <v>-837.4282990933334</v>
+        <v>-849.4771131733335</v>
       </c>
       <c r="Q99">
-        <v>-505.8282990933334</v>
+        <v>-517.8771131733336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7636538325574818</v>
+        <v>1.122580748836222</v>
       </c>
       <c r="T99">
-        <v>13.99230733718122</v>
+        <v>20.98846100577183</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05669491824456984</v>
+        <v>0.05611639867064565</v>
       </c>
       <c r="W99">
-        <v>0.2224313382779304</v>
+        <v>0.2225677531934618</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2834745912228491</v>
+        <v>0.2805819933532282</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.240568013106317</v>
+        <v>0.242468013106317</v>
       </c>
       <c r="C100">
-        <v>-5249.077150240046</v>
+        <v>-5319.632391677143</v>
       </c>
       <c r="D100">
-        <v>691.7788497599544</v>
+        <v>685.0956083228562</v>
       </c>
       <c r="E100">
-        <v>3521.356</v>
+        <v>3585.228</v>
       </c>
       <c r="F100">
-        <v>6259.456</v>
+        <v>6323.328</v>
       </c>
       <c r="G100">
         <v>318.6</v>
@@ -9481,37 +9481,37 @@
         <v>414.1333333333333</v>
       </c>
       <c r="M100">
-        <v>1475.9797248</v>
+        <v>1491.0407424</v>
       </c>
       <c r="N100">
-        <v>-1061.846391466667</v>
+        <v>-1076.907409066667</v>
       </c>
       <c r="O100">
-        <v>-212.3692782933334</v>
+        <v>-215.3814818133334</v>
       </c>
       <c r="P100">
-        <v>-849.4771131733335</v>
+        <v>-861.5259272533334</v>
       </c>
       <c r="Q100">
-        <v>-517.8771131733336</v>
+        <v>-529.9259272533334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.122580748836222</v>
+        <v>2.199361497672445</v>
       </c>
       <c r="T100">
-        <v>20.98846100577183</v>
+        <v>41.97692201154366</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05611639867064565</v>
+        <v>0.05554956636084116</v>
       </c>
       <c r="W100">
-        <v>0.2225677531934618</v>
+        <v>0.2227014122521137</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2805819933532282</v>
+        <v>0.2777478318042057</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.242468013106317</v>
-      </c>
-      <c r="C101">
-        <v>-5319.632391677143</v>
-      </c>
-      <c r="D101">
-        <v>685.0956083228562</v>
-      </c>
-      <c r="E101">
-        <v>3585.228</v>
-      </c>
-      <c r="F101">
-        <v>6323.328</v>
-      </c>
-      <c r="G101">
-        <v>318.6</v>
-      </c>
-      <c r="H101">
-        <v>3649.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>745.7333333333332</v>
-      </c>
-      <c r="K101">
-        <v>331.6</v>
-      </c>
-      <c r="L101">
-        <v>414.1333333333333</v>
-      </c>
-      <c r="M101">
-        <v>1491.0407424</v>
-      </c>
-      <c r="N101">
-        <v>-1076.907409066667</v>
-      </c>
-      <c r="O101">
-        <v>-215.3814818133334</v>
-      </c>
-      <c r="P101">
-        <v>-861.5259272533334</v>
-      </c>
-      <c r="Q101">
-        <v>-529.9259272533334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.199361497672445</v>
-      </c>
-      <c r="T101">
-        <v>41.97692201154366</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05554956636084116</v>
-      </c>
-      <c r="W101">
-        <v>0.2227014122521137</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2777478318042057</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
